--- a/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
+++ b/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
@@ -27140,7 +27140,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS cùng GV lật mục lục sách điện tử trên tivi, chỉ được các phần Unit, Lesson của sách.</t>
+          <t>Digital competence 1.1 CB2c: Pupils go through the table of contents of the e-book on the TV with the teacher and point out the Units and Lessons of the book.</t>
         </is>
       </c>
     </row>
@@ -27174,8 +27174,8 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Mở đầu bài “Hello again”, GV chỉ vào máy chiếu và hỏi What should we do when we use the big screen?
-Năng lực số Miền 1 (Cơ bản, bậc 2): GV bật bản ghi âm bản ngữ đoạn Ms Hoa chào và giới thiệu các bạn trong lớp, cho nghe hai lần; HS nghe và tích đúng tranh trên màn hình</t>
+          <t>Digital competence Domain 2 (Basic, level 2): At the start of the lesson “Hello again”, the teacher points to the projector and asks What should we do when we use the big screen?
+Digital competence Domain 1 (Basic, level 2): The teacher plays the native-speaker audio of Ms Hoa greeting and introducing the pupils in the class twice; pupils listen and tick the right picture on the screen</t>
         </is>
       </c>
     </row>
@@ -27209,8 +27209,8 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trong bài “Classroom activities”, GV bật ghi âm bản ngữ bốn câu tả các bạn đang làm gì trong lớp giờ ra chơi như reading a book, drawing a picture, playing chess; HS nghe
-Năng lực số Miền 3 (Cơ bản, bậc 2): Sau khi tập chant, GV dùng điện thoại quay nhóm HS diễn chant kèm động tác read a book, draw a picture rồi chiếu ngay lên tivi; lớp nhận xét nhóm nào đọc rõ</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the lesson “Classroom activities”, the teacher plays native-speaker audio of four sentences describing what friends are doing in class at break time, such as reading a book, drawing a picture, playing chess; pupils listen
+Digital competence Domain 3 (Basic, level 2): After practising the chant, the teacher uses a phone to film groups of pupils performing the chant with the actions read a book, draw a picture and shows it on the TV straight away; the class comments on which group speaks clearly</t>
         </is>
       </c>
     </row>
@@ -27244,8 +27244,8 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu flashcard số các hoạt động ngoài trời trong bài “Outdoor activities”: skipping, playing football, playing badminton, flying a kite, riding a bike; HS nhìn tranh
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV tổ chức trò chơi nghe–chọn tranh trên màn hình: bật ghi âm I like flying a kite. / She likes skipping., HS chọn tranh đúng</t>
+          <t>Digital competence Domain 1 (Basic, level 2): The teacher shows digital flashcards of outdoor activities in the lesson “Outdoor activities”: skipping, playing football, playing badminton, flying a kite, riding a bike; pupils look at the pictures
+Digital competence Domain 5 (Basic, level 2): The teacher organises a listen-and-choose-the-picture game on the screen: the teacher plays the recording I like flying a kite. / She likes skipping., and pupils choose the right picture</t>
         </is>
       </c>
     </row>
@@ -27279,8 +27279,8 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS quan sát flashcard số trên màn hình rồi hỏi – đáp theo cặp về tên nước, quốc tịch của bạn.
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence 2.1 CB2a: Pupils look at digital flashcards on the screen, then ask and answer in pairs about their friends’ countries and nationalities.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27348,9 +27348,9 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Trong bài “My friends — Lesson 2 (1-3)”, GV chiếu tranh các cách làm quen với bạn ở xa: gặp trực tiếp, gọi video có người lớn bên cạnh
-Năng lực số Miền 1 (Cơ bản, bậc 2): GV bật ghi âm bản ngữ hai tình huống hỏi đáp Where’s he / she from?, dừng sau từng câu để HS nhắc lại; GV chiếu flashcard số các bạn Tony, Linda
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 2 (Basic, level 2): In the lesson “My friends — Lesson 2 (1-3)”, the teacher shows pictures of ways to get to know friends far away: meeting in person, video calling with an adult nearby
+Digital competence Domain 1 (Basic, level 2): The teacher plays native-speaker audio of two situations with Where’s he / she from?, pausing after each sentence for pupils to repeat; the teacher shows digital flashcards of Tony, Linda
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27384,7 +27384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27418,9 +27418,9 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 1 My friends, GV mở tệp ghi âm phần hội thoại hỏi bạn đến từ đâu, chiếu tranh kèm lời thoại lên màn hình
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp theo cặp của HS rồi mở lại; các em nghe và tự đánh giá theo hai tiêu chí chiếu trên màn hình là nói đủ câu và phát…
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In Unit 1 My friends, the teacher plays the audio file of the dialogue asking where a friend is from and shows the picture with the dialogue on the screen
+Digital competence Domain 2 (Basic, level 2): The teacher records pupils' pair exchanges and plays them back; pupils listen and assess themselves using the two criteria shown on the screen, full sentences and clear…
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27454,8 +27454,8 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS quan sát flashcard số trên màn hình rồi hỏi – đáp theo cặp về tên nước, quốc tịch của bạn.
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence 2.1 CB2a: Pupils look at digital flashcards on the screen, then ask and answer in pairs about their friends’ countries and nationalities.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27489,9 +27489,9 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 2 Time and daily routines, GV chiếu mặt đồng hồ số cùng tranh sinh hoạt trong ngày và mở tệp ghi âm mẫu câu hỏi giờ, trả lời giờ
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng thời gian biểu trống của lớp lên màn hình; từng cặp HS hỏi đáp giờ bạn thức dậy, đi học, ăn tối rồi đọc để GV điền vào bảng
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 2 Time and daily routines, the teacher shows a digital clock face with pictures of daily activities and plays the model audio files of asking and telling the time
+Digital competence Domain 2 (Basic, level 2): The teacher shows the class's blank daily timetable on the screen; each pair of pupils asks and answers about the time they get up, go to school and have dinner, then reads it out for the teacher to fill in the table
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27525,9 +27525,9 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 2 Time and daily routines, GV chiếu bộ tranh việc làm trong ngày kèm mặt đồng hồ và mở tệp ghi âm mẫu
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe và chọn tranh đúng, kéo kim đồng hồ về giờ vừa nghe; máy chấm ngay nên HS nhận ra mình còn nhầm giờ hơn với giờ kém
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In Unit 2 Time and daily routines, the teacher shows a set of pictures of daily activities with clock faces and plays the model audio
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise to listen and choose the right picture and drag the clock hands to the time heard; the computer marks it instantly, so pupils notice when they still confuse times with past and times with to
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27561,9 +27561,9 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 2 Time and daily routines, GV chiếu bộ tranh việc làm trong ngày kèm mặt đồng hồ và mở tệp ghi âm mẫu
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe và chọn tranh đúng, kéo kim đồng hồ về giờ vừa nghe; máy chấm ngay nên HS nhận ra mình còn nhầm giờ hơn với giờ kém
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In Unit 2 Time and daily routines, the teacher shows a set of pictures of daily activities with clock faces and plays the model audio
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise to listen and choose the right picture and drag the clock hands to the time heard; the computer marks it instantly, so pupils notice when they still confuse times with past and times with to
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27597,7 +27597,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27631,9 +27631,9 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện nói của bài Unit 2 Time and daily routines, GV chiếu bảng thời gian biểu trống của lớp; từng cặp HS hỏi đáp giờ bạn thức dậy, đi học
-Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một thời gian biểu bằng hình: chọn biểu tượng việc làm, ghi giờ bên cạnh và viết hai câu tiếng Anh giới thiệu
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 2 (Basic, level 2): In the speaking part of Unit 2 Time and daily routines, the teacher shows the class's blank timetable; pairs of pupils ask and answer about what time their partner gets up and goes to school
+Digital competence Domain 3 (Basic, level 2): Each group makes a picture daily schedule: choose activity icons, write the times next to them and write two sentences in English to introduce it
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27667,9 +27667,9 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 2 Time and daily routines, GV chiếu mặt đồng hồ số cùng tranh sinh hoạt trong ngày và mở tệp ghi âm mẫu câu hỏi giờ, trả lời giờ
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng thời gian biểu trống của lớp lên màn hình; từng cặp HS hỏi đáp giờ bạn thức dậy, đi học, ăn tối rồi đọc để GV điền vào bảng
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 2 Time and daily routines, the teacher shows a digital clock face with pictures of daily activities and plays the model audio files of asking and telling the time
+Digital competence Domain 2 (Basic, level 2): The teacher shows the class's blank daily timetable on the screen; each pair of pupils asks and answers about the time they get up, go to school and have dinner, then reads it out for the teacher to fill in the table
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27703,9 +27703,9 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 3 My week, GV chiếu bộ thẻ các thứ trong tuần kèm tệp ghi âm; HS nghe rồi sắp các thứ theo đúng thứ tự trên màn hình
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền thứ còn thiếu vào câu; máy chấm ngay nên HS nhận ra mình còn nhầm hai thứ có cách đọc gần giống nhau
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 3 My week, the teacher shows a set of cards for the days of the week with audio files; pupils listen, then put the days in the right order on the screen
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing days in sentences; the computer marks it instantly, so pupils notice when they still confuse two days that sound alike
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27739,9 +27739,9 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần luyện âm của bài Unit 3 My week, GV mở tệp ghi âm từ và câu chứa âm u, phát chậm rồi phát bình thường; HS nghe
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe rồi chọn từ có chứa âm vừa học và nối câu với tranh; máy chấm ngay nên HS nhận ra mình còn nhầm từ nào
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the pronunciation part of Unit 3 My week, the teacher plays the audio file of words and sentences with the sound u, first slowly and then at normal speed; pupils listen
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the words with the new sound, and match sentences with pictures; the computer marks it instantly, so pupils notice which words they still confuse
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27775,9 +27775,9 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở bài Unit 3 My week phần luyện nói, GV chiếu thời khoá biểu trống của lớp trên màn hình; từng cặp HS hỏi đáp bằng tiếng Anh xem thứ mấy có môn gì
-Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu tuần học của mình: chọn biểu tượng môn học, ghi thứ bên cạnh và viết hai câu tiếng Anh
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 2 (Basic, level 2): In Unit 3 My week, speaking part, the teacher shows the class's blank timetable on the screen; each pair asks and answers in English about which subjects they have on which day
+Digital competence Domain 3 (Basic, level 2): Each group makes a page introducing their school week: choose subject icons, write the days next to them and write two sentences in English
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27845,9 +27845,9 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần luyện âm của bài Unit 3 My week, GV mở tệp ghi âm từ và câu chứa âm u, phát chậm rồi phát bình thường; HS nghe
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe rồi chọn từ có chứa âm vừa học và nối câu với tranh; máy chấm ngay nên HS nhận ra mình còn nhầm từ nào
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the pronunciation part of Unit 3 My week, the teacher plays the audio file of words and sentences with the sound u, first slowly and then at normal speed; pupils listen
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the words with the new sound, and match sentences with pictures; the computer marks it instantly, so pupils notice which words they still confuse
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27881,9 +27881,9 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 3 My week, GV chiếu bộ thẻ các thứ trong tuần kèm tệp ghi âm; HS nghe rồi sắp các thứ theo đúng thứ tự trên màn hình
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền thứ còn thiếu vào câu; máy chấm ngay nên HS nhận ra mình còn nhầm hai thứ có cách đọc gần giống nhau
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 3 My week, the teacher shows a set of cards for the days of the week with audio files; pupils listen, then put the days in the right order on the screen
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing days in sentences; the computer marks it instantly, so pupils notice when they still confuse two days that sound alike
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27917,9 +27917,9 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 4 My birthday party, GV chiếu tranh bữa tiệc sinh nhật kèm tệp ghi âm mẫu; HS nghe rồi chỉ đúng đồ vật, hoạt động trong tranh
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát ngày sinh nhật của lớp theo tháng; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền vào bảng
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 4 My birthday party, the teacher shows a picture of a birthday party with model audio; pupils listen and point to the right things and activities in the picture
+Digital competence Domain 2 (Basic, level 2): The teacher shows the class survey table of birthdays by month; each pair asks and answers in English and then reads out the answers for the teacher to fill in the table
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27953,7 +27953,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -27987,9 +27987,9 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 4 My birthday party, GV chiếu bộ tranh đồ vật và hoạt động trong bữa tiệc kèm tệp ghi âm; HS nghe rồi nối từ với tranh
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh đúng và điền từ còn thiếu vào lời mời; máy chấm ngay nên HS nhận ra mình còn nhầm hai từ gần giống nhau
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In Unit 4 My birthday party, the teacher shows a set of pictures of things and activities at a party with an audio recording; pupils listen and match the words with the pictures
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the right picture, and fill in the missing words in invitations; the computer marks it instantly, so pupils notice when they still confuse two similar words
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28023,9 +28023,9 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 4 My birthday party, GV chiếu bộ tranh đồ vật và hoạt động trong bữa tiệc kèm tệp ghi âm; HS nghe rồi nối từ với tranh
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh đúng và điền từ còn thiếu vào lời mời; máy chấm ngay nên HS nhận ra mình còn nhầm hai từ gần giống nhau
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In Unit 4 My birthday party, the teacher shows a set of pictures of things and activities at a party with an audio recording; pupils listen and match the words with the pictures
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the right picture, and fill in the missing words in invitations; the computer marks it instantly, so pupils notice when they still confuse two similar words
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28059,9 +28059,9 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần luyện âm và nghe của bài Unit 4 My birthday party, GV mở tệp ghi âm phát chậm rồi phát bình thường; HS nghe
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp về bữa tiệc sinh nhật của vài cặp rồi mở cho cả lớp nghe; HS nhận xét theo tiêu chí nói đủ câu, phát âm rõ
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the pronunciation and listening part of Unit 4 My birthday party, the teacher plays the audio file slowly and then at normal speed; pupils listen
+Digital competence Domain 2 (Basic, level 2): The teacher records a few pairs asking and answering about a birthday party and plays it for the whole class; pupils comment using the criteria of full sentences and clear pronunciation
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28095,7 +28095,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28129,9 +28129,9 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 5 Things we can do, GV chiếu bộ tranh hoạt động kèm tệp ghi âm mẫu; HS nghe rồi nối việc làm với tranh
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng ba cột tên bạn, việc bạn làm được và việc bạn muốn học; từng cặp hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 5 Things we can do, the teacher shows a set of activity pictures with model audio; pupils listen and match the activities with the pictures
+Digital competence Domain 2 (Basic, level 2): The teacher shows a three-column table of friends' names, what they can do and what they want to learn; each pair asks and answers in English and then reads out the answers for the teacher to fill in
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28165,9 +28165,9 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 5 Things we can do, GV mở bài hát và học liệu của bài trên kho học liệu số của ngành rồi chỉ cho HS thấy đường…
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền từ còn thiếu vào câu; máy chấm ngay nên HS nhận ra mình còn nhầm chỗ nào, nghe lại đoạn đó
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the skills part of Unit 5 Things we can do, the teacher opens the song and learning materials of the lesson in the education sector's digital learning resource library and shows pupils the way…
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing words in sentences; the computer marks it instantly, so pupils notice where they went wrong and listen to that part again
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28201,9 +28201,9 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 5 Things we can do, GV mở bài tập tương tác nghe chọn tranh và điền từ còn thiếu vào câu nói về khả năng
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp của vài cặp rồi mở cho cả lớp nghe; HS nhận xét theo tiêu chí nói đủ câu, phát âm rõ, dùng đúng mẫu câu
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 5 (Basic, level 2): In the practice part of Unit 5 Things we can do, the teacher opens an interactive exercise: listen and choose the picture and fill in the missing words in sentences about abilities
+Digital competence Domain 2 (Basic, level 2): The teacher records the exchanges of a few pairs and plays them to the class; pupils comment using the criteria: full sentences, clear pronunciation, correct patterns
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28237,7 +28237,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28271,9 +28271,9 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 5 Things we can do, GV mở bài hát và học liệu của bài trên kho học liệu số của ngành rồi chỉ cho HS thấy đường…
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền từ còn thiếu vào câu; máy chấm ngay nên HS nhận ra mình còn nhầm chỗ nào, nghe lại đoạn đó
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the skills part of Unit 5 Things we can do, the teacher opens the song and learning materials of the lesson in the education sector's digital learning resource library and shows pupils the way…
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing words in sentences; the computer marks it instantly, so pupils notice where they went wrong and listen to that part again
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28307,9 +28307,9 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 5 Things we can do, GV chiếu bộ tranh hoạt động kèm tệp ghi âm mẫu; HS nghe rồi nối việc làm với tranh
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng ba cột tên bạn, việc bạn làm được và việc bạn muốn học; từng cặp hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 5 Things we can do, the teacher shows a set of activity pictures with model audio; pupils listen and match the activities with the pictures
+Digital competence Domain 2 (Basic, level 2): The teacher shows a three-column table of friends' names, what they can do and what they want to learn; each pair asks and answers in English and then reads out the answers for the teacher to fill in
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28343,8 +28343,8 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết Review 1 phần nghe và đọc, GV mở bộ bài tập tương tác tổng hợp các chủ điểm đã học; sau mỗi câu máy báo đúng
-Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bảng tổng hợp từ vựng và mẫu câu của các bài đã học, bấm sáng dần từng nhóm; HS nhìn bảng để nhớ lại theo chủ điểm chứ không học rời rạc</t>
+          <t>Digital competence Domain 5 (Basic, level 2): In Review 1, listening and reading part, the teacher opens a set of interactive exercises covering the topics learnt; after each question the computer shows whether the answer is correct
+Digital competence Domain 1 (Basic, level 2): The teacher shows a summary table of the vocabulary and sentence patterns from the lessons learnt, highlighting each group in turn; pupils look at the table to recall them by topic rather than as separate items</t>
         </is>
       </c>
     </row>
@@ -28378,8 +28378,8 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở tiết Review 1 phần nói và viết, GV chiếu bảng ghi câu trả lời của các nhóm lên màn hình theo từng chủ điểm
-Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang ôn tập nhỏ: chọn hình minh hoạ cho ba chủ điểm đã học, ghi từ khoá và một mẫu câu</t>
+          <t>Digital competence Domain 2 (Basic, level 2): In the speaking and writing part of Review 1, the teacher shows a table of the groups' answers on the screen by topic
+Digital competence Domain 3 (Basic, level 2): Each group makes a small review page: choose pictures for three topics learnt, write key words and a sentence pattern</t>
         </is>
       </c>
     </row>
@@ -28413,8 +28413,8 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết hoạt động mở rộng, GV mở bộ bài tập tương tác tổng hợp các chủ điểm đã học; sau mỗi câu máy báo đúng
-Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trò chơi ôn tập nhỏ trên giấy hoặc trên máy: viết năm câu hỏi kèm đáp án theo chủ điểm đã học</t>
+          <t>Digital competence Domain 5 (Basic, level 2): In the extension activity lesson, the teacher opens a set of interactive exercises covering the topics learnt; after each question the computer shows right
+Digital competence Domain 3 (Basic, level 2): Each group makes a small review game on paper or on the computer: write five questions with answers on the topics learnt</t>
         </is>
       </c>
     </row>
@@ -28448,9 +28448,9 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 6 Our school facilities, GV chiếu ảnh các phòng chức năng của trường kèm tệp ghi âm mẫu; HS nghe rồi nối tên phòng với ảnh
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng liệt kê phòng chức năng của trường; từng cặp HS hỏi đáp bằng tiếng Anh xem trường mình có phòng nào rồi đọc để thầy cô đánh dấu
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 6 Our school facilities, the teacher shows photos of the school's special rooms with model audio files; pupils listen, then match the room names with the photos
+Digital competence Domain 2 (Basic, level 2): The teacher shows a table listing the school's facilities; each pair asks and answers in English about which rooms their school has and then reads out the answers for the teacher to tick
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28484,7 +28484,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28518,9 +28518,9 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở bài Unit 6 phần luyện tập, GV mở bài tập tương tác nghe chọn tranh và ghép câu hỏi với câu trả lời về phòng chức năng
-Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu trường mình bằng tiếng Anh: chọn ba ảnh phòng chức năng, ghi tên và viết một câu về hoạt động ở đó
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 5 (Basic, level 2): In the practice part of Unit 6, the teacher opens an interactive exercise: listen and choose the picture, and match questions with answers about the school facilities
+Digital competence Domain 3 (Basic, level 2): Each group makes a page introducing our school in English: choose three photos of school facilities, write their names and one sentence about the activities there
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28554,7 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28588,9 +28588,9 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 6 Our school facilities, GV mở tệp ghi âm và chiếu tranh kèm từ khoá; HS nghe lần một nắm ý chung
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV mở bài hát của bài học trên màn hình cho cả lớp hát theo, sau đó ghi âm lượt hỏi đáp của vài cặp về phòng chức năng và mở lại để các…
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the skills part of Unit 6 Our school facilities, the teacher plays the audio recording and shows pictures with key words; pupils listen the first time for the general idea
+Digital competence Domain 2 (Basic, level 2): The teacher plays the lesson's song on the screen for the whole class to sing along, then records a few pairs' questions and answers about the school rooms and plays them back so the…
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28624,7 +28624,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28658,9 +28658,9 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 7 Our timetables, GV chiếu thời khoá biểu mẫu kèm tệp ghi âm mẫu; HS nghe rồi chỉ đúng môn học ở đúng thứ trên bảng
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu thời khoá biểu trống của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 7 Our timetables, the teacher shows a sample timetable with model audio; pupils listen and point to the right subject on the right day in the table
+Digital competence Domain 2 (Basic, level 2): The teacher shows a blank class timetable; each pair asks and answers in English and then reads out the answers for the teacher to fill in
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28694,9 +28694,9 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 7, GV mở bài hát của bài học trên màn hình cho cả lớp hát theo rồi ghi âm lượt hỏi đáp về thời khoá biểu của vài…
-Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một thời khoá biểu bằng hình: chọn biểu tượng môn học, ghi thứ và viết hai câu tiếng Anh giới thiệu ngày mình thích nhất
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 2 (Basic, level 2): In the practice part of Unit 7, the teacher plays the lesson's song on the screen for the whole class to sing along, then records the questions and answers about the timetable of a few…
+Digital competence Domain 3 (Basic, level 2): Each group makes a picture timetable: choose subject icons, write the days and two sentences in English introducing their favourite day
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28730,9 +28730,9 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 7 Our timetables, GV chiếu thời khoá biểu mẫu kèm tệp ghi âm; HS nghe rồi chỉ đúng môn học ở đúng thứ
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền tên môn còn thiếu vào thời khoá biểu; máy chấm ngay nên HS nhận ra mình nghe nhầm môn nào
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In Unit 7 Our timetables, the teacher shows a sample timetable with audio files; pupils listen, then point to the right subject on the right day
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing subjects in the timetable; the computer marks it instantly, so pupils notice which subjects they misheard
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28766,7 +28766,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28800,9 +28800,9 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 7, GV mở bài hát của bài học trên màn hình cho cả lớp hát theo rồi ghi âm lượt hỏi đáp về thời khoá biểu của vài…
-Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một thời khoá biểu bằng hình: chọn biểu tượng môn học, ghi thứ và viết hai câu tiếng Anh giới thiệu ngày mình thích nhất
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 2 (Basic, level 2): In the practice part of Unit 7, the teacher plays the lesson's song on the screen for the whole class to sing along, then records the questions and answers about the timetable of a few…
+Digital competence Domain 3 (Basic, level 2): Each group makes a picture timetable: choose subject icons, write the days and two sentences in English introducing their favourite day
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28836,9 +28836,9 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 7, GV mở bài hát của bài học trên màn hình cho cả lớp hát theo rồi ghi âm lượt hỏi đáp về thời khoá biểu của vài…
-Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một thời khoá biểu bằng hình: chọn biểu tượng môn học, ghi thứ và viết hai câu tiếng Anh giới thiệu ngày mình thích nhất
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 2 (Basic, level 2): In the practice part of Unit 7, the teacher plays the lesson's song on the screen for the whole class to sing along, then records the questions and answers about the timetable of a few…
+Digital competence Domain 3 (Basic, level 2): Each group makes a picture timetable: choose subject icons, write the days and two sentences in English introducing their favourite day
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28872,9 +28872,9 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 8 My favourite subjects, GV chiếu bộ tranh các môn học kèm tệp ghi âm mẫu; HS nghe rồi nối tên môn với tranh
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát môn học yêu thích của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 8 My favourite subjects, the teacher shows a set of pictures of school subjects with model audio files; pupils listen, then match the subject names with the pictures
+Digital competence Domain 2 (Basic, level 2): The teacher shows the class survey table of favourite subjects; each pair asks and answers in English and then reads out the answers for the teacher to tick
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28908,7 +28908,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28942,9 +28942,9 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 8, GV mở bài tập tương tác nghe chọn tranh và điền tên môn còn thiếu vào câu
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp về môn học yêu thích của vài cặp rồi mở cho cả lớp nghe; HS nhận xét theo tiêu chí nói đủ câu, phát âm rõ
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 5 (Basic, level 2): In the practice part of Unit 8, the teacher opens an interactive exercise: listen and choose the picture, and fill in the missing subject names in sentences
+Digital competence Domain 2 (Basic, level 2): The teacher records a few pairs asking and answering about their favourite subjects and plays them to the class; pupils comment using the criteria: full sentences, clear pronunciation
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -28978,7 +28978,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29012,9 +29012,9 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 8 My favourite subjects, GV mở bài tập tương tác nghe chọn tranh và điền tên môn còn thiếu vào câu
-Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu môn học yêu thích: chọn hình, ghi tên môn và viết hai câu nêu lí do bằng tiếng Anh
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 5 (Basic, level 2): In the skills part of Unit 8 My favourite subjects, the teacher opens an interactive exercise: listen and choose the picture and fill in the missing subject names in the sentences
+Digital competence Domain 3 (Basic, level 2): Each group makes a page about a favourite subject: choose a picture, write the subject name and write two sentences in English giving reasons
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29048,9 +29048,9 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 8 My favourite subjects, GV chiếu bộ tranh các môn học kèm tệp ghi âm mẫu; HS nghe rồi nối tên môn với tranh
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát môn học yêu thích của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 8 My favourite subjects, the teacher shows a set of pictures of school subjects with model audio files; pupils listen, then match the subject names with the pictures
+Digital competence Domain 2 (Basic, level 2): The teacher shows the class survey table of favourite subjects; each pair asks and answers in English and then reads out the answers for the teacher to tick
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29084,9 +29084,9 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 9 Our sports day, GV chiếu bộ tranh các môn thể thao trong ngày hội thể thao kèm tệp ghi âm mẫu; HS nghe rồi nối tên môn với tranh
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng đăng kí môn thi của lớp trong ngày hội thể thao; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 9 Our sports day, the teacher shows a set of pictures of the sports at sports day with model audio; pupils listen and match the names of the sports with the pictures
+Digital competence Domain 2 (Basic, level 2): The teacher shows the class's sports day registration table; each pair asks and answers in English and then reads out the answers for the teacher to fill in
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29120,7 +29120,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29154,9 +29154,9 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 9 “Our sports day”, GV chiếu tranh các môn thi đấu trong ngày hội thể thao lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Unscramble the letters, GV chiếu các chữ cái bị đảo của tên tháng lên màn hình; các nhóm bàn nhau sắp lại thành từ đúng rồi lên bấm chọn
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 9 “Our sports day”, the teacher shows pictures of the sports day events on the screen and plays the model audio
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Unscramble the letters, the teacher shows the jumbled letters of month names on the screen; groups discuss, put them in the right order and come up to click their choice
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29190,7 +29190,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29224,9 +29224,9 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 9 “Our sports day”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Let's chant, GV mở bản chant có chữ chạy theo nhịp trên màn hình để cả lớp đọc đồng thanh đúng tiết tấu
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 9 “Our sports day”, the teacher shows the pictures on the screen and plays the audio, pausing after each part so pupils tick
+Digital competence Domain 2 (Basic, level 2): In the Let's chant activity, the teacher plays the chant with words moving in rhythm on the screen so the whole class chants together in the right rhythm
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29260,9 +29260,9 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 9 “Our sports day”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Let's chant, GV mở bản chant có chữ chạy theo nhịp trên màn hình để cả lớp đọc đồng thanh đúng tiết tấu
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 9 “Our sports day”, the teacher shows the pictures on the screen and plays the audio, pausing after each part so pupils tick
+Digital competence Domain 2 (Basic, level 2): In the Let's chant activity, the teacher plays the chant with words moving in rhythm on the screen so the whole class chants together in the right rhythm
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29296,9 +29296,9 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 10 “Our summer holidays”, GV chiếu tranh các kì nghỉ hè lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Point and say, GV chiếu bảng chung “Nơi đã đến – Việc đã làm”; các cặp hỏi đáp rồi lên điền câu trả lời của bạn mình vào bảng
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 10 “Our summer holidays”, the teacher shows pictures of summer holidays on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the Point and say activity, the teacher shows a shared table “Places visited – Things done”; pairs ask and answer, then come up to write their partner's answers in the table
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29332,9 +29332,9 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 10 “Our summer holidays”, GV mở bản nghe mẫu âm ere trong từ were
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Board race, GV chiếu chủ đề lên màn hình, hai đội thay nhau viết từ đã học
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 10 “Our summer holidays”, the teacher plays the model audio of the sound ere in the word were
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Board race, the teacher shows the topic on the screen, and two teams take turns writing words they have learnt
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29368,9 +29368,9 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and number của Unit 10 “Our summer holidays”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh số
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát Were you on the beach yesterday? có lời chạy trên màn hình để cả lớp hát đồng thanh
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and number activity of Unit 10 “Our summer holidays”, the teacher shows the pictures on the screen and plays the audio, pausing after each part so pupils can number them
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song Were you on the beach yesterday? with scrolling lyrics on the screen for the whole class to sing together
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29404,7 +29404,7 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29438,9 +29438,9 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 10 “Our summer holidays”, GV mở bản nghe mẫu âm ere trong từ were
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Board race, GV chiếu chủ đề lên màn hình, hai đội thay nhau viết từ đã học
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 10 “Our summer holidays”, the teacher plays the model audio of the sound ere in the word were
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Board race, the teacher shows the topic on the screen, and two teams take turns writing words they have learnt
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29474,9 +29474,9 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 10 “Our summer holidays”, GV chiếu tranh các kì nghỉ hè lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Point and say, GV chiếu bảng chung “Nơi đã đến – Việc đã làm”; các cặp hỏi đáp rồi lên điền câu trả lời của bạn mình vào bảng
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 10 “Our summer holidays”, the teacher shows pictures of summer holidays on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the Point and say activity, the teacher shows a shared table “Places visited – Things done”; pairs ask and answer, then come up to write their partner's answers in the table
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29510,8 +29510,8 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Listen and tick của Review 2, GV chiếu tranh lên màn hình và mở bản nghe năm tình huống giao tiếp, dừng sau mỗi tình huống để HS chọn đáp án
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV chiếu danh sách các bài hát từ Unit 6 đến Unit 10 kèm lời chạy trên màn hình để các nhóm chọn một bài và hát đồng thanh</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick part of Review 2, the teacher shows pictures on the screen and plays the audio of five communication situations, pausing after each situation so pupils choose the answer
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher shows a list of songs from Unit 6 to Unit 10 with scrolling lyrics on the screen so each group chooses one song and sings it together</t>
         </is>
       </c>
     </row>
@@ -29545,8 +29545,8 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Read and match của Review 2, GV chiếu các cặp câu và tranh lên màn hình, cho hiện lần lượt từng cặp để HS đọc, nối thử rồi mở đáp án
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Practice, GV chiếu bảng chung các mẫu câu của Unit 6 đến Unit 10; mỗi nhóm lên đặt một câu theo mẫu và ghi vào bảng</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Read and match part of Review 2, the teacher shows pairs of sentences and pictures on the screen, revealing each pair in turn for pupils to read, try matching and then see the answer
+Digital competence Domain 2 (Basic, level 2): In the Practice part, the teacher shows a shared table of the sentence patterns from Unit 6 to Unit 10; each group comes up to make a sentence following a pattern and writes it in the table</t>
         </is>
       </c>
     </row>
@@ -29580,8 +29580,8 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Read and match của Extension activities 2, GV chiếu hai đoạn đọc về vùng quê và thành phố cùng bộ tranh lên màn hình; HS đọc thầm
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập, GV mở bài tập tương tác điền từ vào chỗ trống của hai đoạn đọc; HS chọn từ rồi bấm kiểm tra</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Read and match of Extension activities 2, the teacher shows two reading texts about the countryside and the city with a set of pictures on the screen; pupils read silently
+Digital competence Domain 5 (Basic, level 2): In the practice part, the teacher opens an interactive exercise to fill in the blanks in two reading texts; pupils choose the words and click to check</t>
         </is>
       </c>
     </row>
@@ -29675,8 +29675,8 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 11 “My home”, GV chiếu tranh các phòng trong nhà lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bản chant về ngôi nhà có chữ chạy theo nhịp; sau khi nghe, các nhóm sắp lại các thẻ từ chỉ phòng theo đúng thứ tự xuất hiện trong…</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 11 “My home”, the teacher shows pictures of the rooms in a house on the screen and plays the model audio
+Digital competence Domain 5 (Basic, level 2): In the Warm-up, the teacher plays a chant about the house with the words moving along to the rhythm; after listening, groups put the room word cards in the order they appear in…</t>
         </is>
       </c>
     </row>
@@ -29710,9 +29710,9 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 11 “My home”, GV mở bản nghe mẫu âm của các chữ cái trong bài
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát My house có lời chạy trên màn hình cho cả lớp hát; sau đó chia hai nhóm hát nối tiếp theo phần lời đang sáng và nghe…
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 11 “My home”, the teacher plays the model audio of the letter sounds in the lesson
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song My house with scrolling lyrics on the screen for the whole class to sing; then divides the class into two groups to sing in turn following the highlighted lyrics and listen…
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29746,9 +29746,9 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 11 “My home”, GV chiếu tranh đồ vật trong nhà kèm từ và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Whispering, sau mỗi lượt truyền tin GV chiếu câu gốc lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 11 “My home”, the teacher shows pictures of things in the house with the words and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the Warm-up game Whispering, after each round of passing the message the teacher shows the original sentence on the screen; the two teams compare what they said with the original
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29782,9 +29782,9 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 11 “My home”, GV chiếu tranh đồ vật trong nhà kèm từ và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Whispering, sau mỗi lượt truyền tin GV chiếu câu gốc lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 11 “My home”, the teacher shows pictures of things in the house with the words and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the Warm-up game Whispering, after each round of passing the message the teacher shows the original sentence on the screen; the two teams compare what they said with the original
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29818,9 +29818,9 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 11 “My home”, GV mở bản nghe mẫu âm của các chữ cái trong bài
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát My house có lời chạy trên màn hình cho cả lớp hát; sau đó chia hai nhóm hát nối tiếp theo phần lời đang sáng và nghe…
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 11 “My home”, the teacher plays the model audio of the letter sounds in the lesson
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song My house with scrolling lyrics on the screen for the whole class to sing; then divides the class into two groups to sing in turn following the highlighted lyrics and listen…
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29854,9 +29854,9 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 11 “My home”, GV mở bản nghe mẫu âm của các chữ cái trong bài
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát My house có lời chạy trên màn hình cho cả lớp hát; sau đó chia hai nhóm hát nối tiếp theo phần lời đang sáng và nghe…
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 11 “My home”, the teacher plays the model audio of the letter sounds in the lesson
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song My house with scrolling lyrics on the screen for the whole class to sing; then divides the class into two groups to sing in turn following the highlighted lyrics and listen…
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29890,9 +29890,9 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 12 “Jobs”, GV chiếu tranh những người đang làm việc kèm tên nghề lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the job, GV chiếu lần lượt ảnh một đồ vật gắn với nghề như ống nghe, thước thợ, bảng phấn
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 12 “Jobs”, the teacher shows pictures of people at work with the job names on the screen and plays the model audio
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Guess the job, the teacher shows photos of objects linked to jobs one by one, such as a stethoscope, a builder's ruler, a chalkboard
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29926,9 +29926,9 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 12 “Jobs”, GV chiếu tranh những người đang làm việc kèm tên nghề lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the job, GV chiếu lần lượt ảnh một đồ vật gắn với nghề như ống nghe, thước thợ, bảng phấn
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 12 “Jobs”, the teacher shows pictures of people at work with the job names on the screen and plays the model audio
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Guess the job, the teacher shows photos of objects linked to jobs one by one, such as a stethoscope, a builder's ruler, a chalkboard
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29962,9 +29962,9 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 12 “Jobs”, GV chiếu tranh nơi làm việc kèm từ mới lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện nói, GV chiếu bảng chung “Nghề – Nơi làm việc – Câu nói bằng tiếng Anh”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 12 “Jobs”, the teacher shows pictures of workplaces with the new words on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking part, the teacher shows the shared table “Job – Workplace – Sentence in English”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -29998,9 +29998,9 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 12 “Jobs”, GV mở bản nghe mẫu các từ chỉ nghề, cho nghe chậm rồi nghe lại tốc độ thường và chiếu chữ có đánh dấu…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Lip-reading, GV chiếu từ chỉ nghề riêng cho bạn nhìn, bạn nói không thành tiếng để nhóm đoán
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 12 “Jobs”, the teacher plays the model audio of the job words, first slowly and then at normal speed, and shows the words with marks…
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Lip-reading, the teacher shows a job word to one pupil only, who mouths it silently for the group to guess
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30034,9 +30034,9 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 12 “Jobs”, GV mở bản nghe mẫu các từ chỉ nghề, cho nghe chậm rồi nghe lại tốc độ thường và chiếu chữ có đánh dấu…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Lip-reading, GV chiếu từ chỉ nghề riêng cho bạn nhìn, bạn nói không thành tiếng để nhóm đoán
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 12 “Jobs”, the teacher plays the model audio of the job words, first slowly and then at normal speed, and shows the words with marks…
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Lip-reading, the teacher shows a job word to one pupil only, who mouths it silently for the group to guess
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30070,9 +30070,9 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 12 “Jobs”, GV chiếu tranh những người đang làm việc kèm tên nghề lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the job, GV chiếu lần lượt ảnh một đồ vật gắn với nghề như ống nghe, thước thợ, bảng phấn
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 12 “Jobs”, the teacher shows pictures of people at work with the job names on the screen and plays the model audio
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Guess the job, the teacher shows photos of objects linked to jobs one by one, such as a stethoscope, a builder's ruler, a chalkboard
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30106,9 +30106,9 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 13 “Appearance”, GV chiếu tranh các nhân vật với ngoại hình khác nhau và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nhân vật – Đặc điểm ngoại hình”; các cặp hỏi đáp về nhân vật trong tranh rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 13 “Appearance”, the teacher shows pictures of characters with different appearances and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Character – Appearance”; pairs ask and answer about the characters in the picture and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30142,9 +30142,9 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 13 “Appearance”, GV chiếu tranh các nhân vật với ngoại hình khác nhau và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nhân vật – Đặc điểm ngoại hình”; các cặp hỏi đáp về nhân vật trong tranh rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 13 “Appearance”, the teacher shows pictures of characters with different appearances and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Character – Appearance”; pairs ask and answer about the characters in the picture and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30178,9 +30178,9 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 13 “Appearance”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu người được tả
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do your parents look like? có lời chạy trên màn hình cho cả lớp hát
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 13 “Appearance”, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the person described
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song What do your parents look like? with scrolling lyrics on the screen for the whole class to sing
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30214,9 +30214,9 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 13 “Appearance”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu người được tả
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do your parents look like? có lời chạy trên màn hình cho cả lớp hát
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 13 “Appearance”, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the person described
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song What do your parents look like? with scrolling lyrics on the screen for the whole class to sing
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30250,9 +30250,9 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 13 “Appearance”, GV mở bản nghe mẫu các câu mô tả ngoại hình
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi truyền tin, sau mỗi lượt GV chiếu câu gốc mô tả một người lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 13 “Appearance”, the teacher plays the model audio of sentences describing appearance
+Digital competence Domain 5 (Basic, level 2): In the Warm-up message-passing game, after each turn the teacher shows the original sentence describing a person on the screen; the two teams compare what they said with the original sentence
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30286,9 +30286,9 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 13 “Appearance”, GV mở bản nghe mẫu các câu mô tả ngoại hình
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi truyền tin, sau mỗi lượt GV chiếu câu gốc mô tả một người lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 13 “Appearance”, the teacher plays the model audio of sentences describing appearance
+Digital competence Domain 5 (Basic, level 2): In the Warm-up message-passing game, after each turn the teacher shows the original sentence describing a person on the screen; the two teams compare what they said with the original sentence
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30322,9 +30322,9 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm hằng ngày kèm từ mới lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Giờ – Việc em làm”; các cặp hỏi đáp về thời gian biểu của nhau rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Time – What I do”; pairs ask and answer about each other's daily timetables, then come up to write their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30358,9 +30358,9 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm hằng ngày kèm từ mới lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Giờ – Việc em làm”; các cặp hỏi đáp về thời gian biểu của nhau rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Time – What I do”; pairs ask and answer about each other's daily timetables, then come up to write their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30394,9 +30394,9 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm trong ngày kèm từ mới lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Change chairs, GV chiếu câu lệnh lên màn hình để cả lớp cùng đọc; HS nghe và đổi chỗ nếu câu đúng với mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the Warm-up game Change chairs, the teacher shows the commands on the screen for the whole class to read together; pupils listen and change seats if the sentence is true for them
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30430,9 +30430,9 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm trong ngày kèm từ mới lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Change chairs, GV chiếu câu lệnh lên màn hình để cả lớp cùng đọc; HS nghe và đổi chỗ nếu câu đúng với mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the Warm-up game Change chairs, the teacher shows the commands on the screen for the whole class to read together; pupils listen and change seats if the sentence is true for them
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30466,9 +30466,9 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 14 “Daily activities”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Spelling Bee, GV chiếu từ đã học lên màn hình rồi che đi, các nhóm đánh vần lại
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 14 “Daily activities”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Spelling Bee, the teacher shows learnt words on the screen and then hides them; groups spell them again
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30502,9 +30502,9 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm hằng ngày kèm từ mới lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Giờ – Việc em làm”; các cặp hỏi đáp về thời gian biểu của nhau rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Time – What I do”; pairs ask and answer about each other's daily timetables, then come up to write their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30538,9 +30538,9 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 15 “My family's weekends”, GV chiếu tranh các địa điểm trong thị trấn kèm tên gọi lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi đến cuối tuần – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 15 “My family's weekends”, the teacher shows pictures of places in the town with their names on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Weekend places – What people do there”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30574,9 +30574,9 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 15 “My family's weekends”, GV chiếu tranh các địa điểm trong thị trấn kèm tên gọi lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi đến cuối tuần – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 15 “My family's weekends”, the teacher shows pictures of places in the town with their names on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Weekend places – What people do there”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30610,9 +30610,9 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 15, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu nơi gia đình bạn nhỏ đến
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát Where do they go on Saturdays? có lời chạy trên màn hình cho cả lớp hát
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 15, the teacher shows the pictures on the screen and plays the audio, pausing after each part so pupils can tick the places the child's family goes to
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song Where do they go on Saturdays? with scrolling lyrics on the screen for the whole class to sing
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30646,7 +30646,7 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30680,9 +30680,9 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 15 “My family's weekends”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu trọng âm…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Matching, GV chiếu hai cột từ và tranh bị xáo trộn; các nhóm nối thử rồi bấm kiểm tra
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 15 “My family's weekends”, the teacher plays the model audio, first slowly and then at normal speed, and shows the sentences with stress marks…
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Matching, the teacher shows two shuffled columns of words and pictures; groups try matching them and then click check
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30716,9 +30716,9 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 15 “My family's weekends”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu trọng âm…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Matching, GV chiếu hai cột từ và tranh bị xáo trộn; các nhóm nối thử rồi bấm kiểm tra
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 15 “My family's weekends”, the teacher plays the model audio, first slowly and then at normal speed, and shows the sentences with stress marks…
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Matching, the teacher shows two shuffled columns of words and pictures; groups try matching them and then click check
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30752,9 +30752,9 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Listen and tick của Review 3, GV chiếu tranh lên màn hình và mở bản nghe các tình huống giao tiếp đã học, dừng sau mỗi tình huống để HS chọn
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát và bản chant của Unit 15 có lời chạy trên màn hình; các nhóm chọn một bài
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick part of Review 3, the teacher shows the pictures on the screen and plays the audio of the communication situations learnt, pausing after each situation so pupils can choose
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song and the chant of Unit 15 with scrolling lyrics on the screen; each group chooses one
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30788,8 +30788,8 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Fun time của Review 3, GV chiếu lần lượt các từ và câu đã học lên màn hình cho HS đọc nối tiếp
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập, GV mở bài tập tương tác nối câu hỏi với câu trả lời; HS chọn rồi bấm kiểm tra</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Fun time part of Review 3, the teacher shows the learnt words and sentences on the screen one by one for pupils to read in turn
+Digital competence Domain 5 (Basic, level 2): In the practice stage, the teacher opens an interactive exercise to match questions with answers; pupils choose and click check</t>
         </is>
       </c>
     </row>
@@ -30853,8 +30853,8 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 16 “Weather”, GV chiếu tranh các kiểu thời tiết kèm từ mới lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi – Thời tiết hôm nay – Câu nói bằng tiếng Anh”; các cặp hỏi đáp rồi lên điền</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 16 “Weather”, the teacher shows pictures of types of weather with the new words on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Place – Today's weather – Sentence in English”; pairs ask and answer, then come up to fill it in</t>
         </is>
       </c>
     </row>
@@ -30888,7 +30888,7 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30922,9 +30922,9 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 16 “Weather”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu kiểu thời tiết
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What was the weather like? có lời chạy trên màn hình cho cả lớp hát
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 16 “Weather”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick the type of weather
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song What was the weather like? with scrolling lyrics on the screen for the whole class to sing
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30958,7 +30958,7 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30992,9 +30992,9 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 16 “Weather”, GV mở bản nghe mẫu hai âm được học, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu ví dụ có…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Slap the board, GV chiếu các từ đã học lên màn hình; hai đội nghe GV đọc rồi lên chạm đúng từ
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 16 “Weather”, the teacher plays the model audio of the two sounds learnt, first slowly and then at normal speed, and shows example sentences with…
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Slap the board, the teacher shows the words learnt on the screen; two teams listen to the teacher and come up to touch the right word
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31028,9 +31028,9 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 16 “Weather”, GV mở bản nghe mẫu hai âm được học, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu ví dụ có…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Slap the board, GV chiếu các từ đã học lên màn hình; hai đội nghe GV đọc rồi lên chạm đúng từ
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 16 “Weather”, the teacher plays the model audio of the two sounds learnt, first slowly and then at normal speed, and shows example sentences with…
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Slap the board, the teacher shows the words learnt on the screen; two teams listen to the teacher and come up to touch the right word
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31064,9 +31064,9 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu tranh các địa điểm trong thành phố kèm tên gọi lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Địa điểm – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 17 “In the city”, the teacher shows pictures of places in the city with their names on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Place – What people do there”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31100,9 +31100,9 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 17 “In the city”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu nơi được nhắc tới
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Memory game, GV chiếu bộ thẻ từ chỉ đường và địa điểm rồi giấu dần từng thẻ; các nhóm nhớ và gọi tên thẻ đã mất
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 17 “In the city”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick the places mentioned
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Memory game, the teacher shows a set of cards with direction and place words and then hides them one by one; groups remember and name the missing card
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31136,9 +31136,9 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu sơ đồ đường phố lên màn hình và mở bản nghe mẫu các câu chỉ đường
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bản đồ khu phố có đánh dấu điểm xuất phát và đích đến; các cặp thay nhau chỉ đường bằng tiếng Anh
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 17 “In the city”, the teacher shows a street map on the screen and plays the model audio of sentences giving directions
+Digital competence Domain 5 (Basic, level 2): In the speaking activity, the teacher shows a neighbourhood map marked with a starting point and a destination; pairs take turns giving directions in English
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31172,9 +31172,9 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu sơ đồ đường phố lên màn hình và mở bản nghe mẫu các câu chỉ đường
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bản đồ khu phố có đánh dấu điểm xuất phát và đích đến; các cặp thay nhau chỉ đường bằng tiếng Anh
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 17 “In the city”, the teacher shows a street map on the screen and plays the model audio of sentences giving directions
+Digital competence Domain 5 (Basic, level 2): In the speaking activity, the teacher shows a neighbourhood map marked with a starting point and a destination; pairs take turns giving directions in English
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31208,9 +31208,9 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 17 “In the city”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu nơi được nhắc tới
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Memory game, GV chiếu bộ thẻ từ chỉ đường và địa điểm rồi giấu dần từng thẻ; các nhóm nhớ và gọi tên thẻ đã mất
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 17 “In the city”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick the places mentioned
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Memory game, the teacher shows a set of cards with direction and place words and then hides them one by one; groups remember and name the missing card
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31244,9 +31244,9 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 17 “In the city”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu nơi được nhắc tới
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Memory game, GV chiếu bộ thẻ từ chỉ đường và địa điểm rồi giấu dần từng thẻ; các nhóm nhớ và gọi tên thẻ đã mất
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 17 “In the city”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick the places mentioned
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Memory game, the teacher shows a set of cards with direction and place words and then hides them one by one; groups remember and name the missing card
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31280,9 +31280,9 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 18 “At the shopping centre”, GV chiếu tranh trung tâm mua sắm kèm tên các gian hàng và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Gian hàng – Thứ mua được ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Look, listen and repeat of Unit 18 “At the shopping centre”, the teacher shows a picture of a shopping centre with the names of the shops and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Shop – Things you can buy there”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31316,9 +31316,9 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 18 “At the shopping centre”, GV chiếu tranh trung tâm mua sắm kèm tên các gian hàng và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Gian hàng – Thứ mua được ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Look, listen and repeat of Unit 18 “At the shopping centre”, the teacher shows a picture of a shopping centre with the names of the shops and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Shop – Things you can buy there”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31352,9 +31352,9 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 18, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần ôn số, GV chiếu các số 20, 50, 80, 90 lên màn hình rồi yêu cầu HS thêm từ thousand và đọc to
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 18, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick
+Digital competence Domain 5 (Basic, level 2): In the number revision part, the teacher shows the numbers 20, 50, 80, 90 on the screen and asks pupils to add the word thousand and read them aloud
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31422,9 +31422,9 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 18 “At the shopping centre”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu chỗ…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the price, GV chiếu ảnh món hàng cùng vài mức giá; các nhóm đoán giá bằng tiếng Anh rồi bấm chọn
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 18 “At the shopping centre”, the teacher plays the model audio, first slowly and then at normal speed, and shows sentences marking the…
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Guess the price, the teacher shows a picture of an item with several prices; groups guess the price in English and click to choose
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31458,9 +31458,9 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 18 “At the shopping centre”, GV chiếu tranh trung tâm mua sắm kèm tên các gian hàng và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Gian hàng – Thứ mua được ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Look, listen and repeat of Unit 18 “At the shopping centre”, the teacher shows a picture of a shopping centre with the names of the shops and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Shop – Things you can buy there”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31494,9 +31494,9 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 19 “The animal world”, GV chiếu tranh các loài vật kèm tên gọi lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Đặc điểm”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the activity Look, listen and repeat of Unit 19 “The animal world”, the teacher shows pictures of animals with their names on the screen and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Animal – Habitat – Features”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31530,9 +31530,9 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 19, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu con vật được nhắc tới
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Thức ăn”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 19, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the animal mentioned
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Animal – Habitat – Food”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31566,9 +31566,9 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 19 “The animal world”, GV chiếu tranh loài vật lên màn hình và mở bản nghe mẫu các câu mô tả
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi đoán con vật, GV chiếu ảnh bị che phần lớn; các nhóm đoán tên bằng tiếng Anh rồi giơ tay trả lời
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 19 “The animal world”, the teacher shows pictures of animals on the screen and plays the model audio of the describing sentences
+Digital competence Domain 5 (Basic, level 2): In the Warm-up animal-guessing game, the teacher shows mostly covered pictures; groups guess the names in English and raise their hands to answer
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31602,9 +31602,9 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 19 “The animal world”, GV chiếu tranh loài vật lên màn hình và mở bản nghe mẫu các câu mô tả
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi đoán con vật, GV chiếu ảnh bị che phần lớn; các nhóm đoán tên bằng tiếng Anh rồi giơ tay trả lời
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 19 “The animal world”, the teacher shows pictures of animals on the screen and plays the model audio of the describing sentences
+Digital competence Domain 5 (Basic, level 2): In the Warm-up animal-guessing game, the teacher shows mostly covered pictures; groups guess the names in English and raise their hands to answer
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31638,9 +31638,9 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 19, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu con vật được nhắc tới
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Thức ăn”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 19, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the animal mentioned
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Animal – Habitat – Food”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31674,9 +31674,9 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 19, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu con vật được nhắc tới
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Thức ăn”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 19, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the animal mentioned
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Animal – Habitat – Food”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31710,9 +31710,9 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 20 “At summer camp”, GV chiếu tranh các hoạt động ở trại hè kèm tên gọi và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Hoạt động ở trại hè – Vì sao em thích”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 20 “At summer camp”, the teacher shows pictures of summer camp activities with their names and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Summer camp activity – Why I like it”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31746,9 +31746,9 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 20 “At summer camp”, GV chiếu tranh các hoạt động ở trại hè kèm tên gọi và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Hoạt động ở trại hè – Vì sao em thích”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 20 “At summer camp”, the teacher shows pictures of summer camp activities with their names and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Summer camp activity – Why I like it”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31782,9 +31782,9 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 20 “At summer camp”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập, GV mở bài tập tương tác nối hoạt động với đồ dùng cần mang theo; HS chọn rồi bấm kiểm tra
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 20 “At summer camp”, the teacher shows the pictures on the screen and plays the audio, pausing after each part so pupils can tick
+Digital competence Domain 5 (Basic, level 2): In the practice part, the teacher opens an interactive exercise to match activities with the things to bring; pupils choose and then click check
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31818,7 +31818,7 @@
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31852,9 +31852,9 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 20 “At summer camp”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu chỗ nhấn…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Lip-reading, GV chiếu từ riêng cho bạn nhìn, bạn nói không thành tiếng để nhóm đoán
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 20 “At summer camp”, the teacher plays the model audio, first slowly and then at normal speed, and shows the sentences with the stressed parts marked…
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Lip-reading, the teacher shows a word to one pupil only, who says it silently for the group to guess
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31888,9 +31888,9 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 20 “At summer camp”, GV chiếu tranh các hoạt động ở trại hè kèm tên gọi và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Hoạt động ở trại hè – Vì sao em thích”; các cặp hỏi đáp rồi lên điền câu của mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 20 “At summer camp”, the teacher shows pictures of summer camp activities with their names and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Summer camp activity – Why I like it”; pairs ask and answer and then come up to fill in their sentences
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31924,9 +31924,9 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Listen and tick của Review 4, GV chiếu tranh lên màn hình và mở bản nghe các tình huống đã học, dừng sau mỗi tình huống để HS chọn
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Choose and throw, GV chiếu các phương án trả lời lên màn hình; hai đội chọn rồi ném bóng dính vào ô mình chọn
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In Listen and tick of Review 4, the teacher shows the pictures on the screen and plays the audio of the situations learnt, pausing after each situation for pupils to choose
+Digital competence Domain 5 (Basic, level 2): In the Warm-up game Choose and throw, the teacher shows the answer options on the screen; two teams choose and throw a sticky ball at the box they choose
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31960,8 +31960,8 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Fun time của Review 4, GV chiếu lần lượt các nhóm từ đã học lên màn hình cho HS đọc và tìm từ khác loại
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập, GV mở bài tập tương tác nối câu hỏi với câu trả lời của các đơn vị đã học; HS chọn rồi bấm kiểm tra</t>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Fun time part of Review 4, the teacher shows groups of learnt words on the screen one by one for pupils to read and find the odd one out
+Digital competence Domain 5 (Basic, level 2): In the practice stage, the teacher opens an interactive exercise to match questions with answers from the units learnt; pupils choose and click check</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
+++ b/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
@@ -8680,11 +8680,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được đặc điểm tạo hình của chạm khắc đình làng qua ảnh phóng to.</t>
-        </is>
-      </c>
+      <c r="H6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -8774,11 +8770,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được cách diễn tả không gian riêng của tranh dân gian.</t>
-        </is>
-      </c>
+      <c r="H9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -8804,11 +8796,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được cách diễn tả không gian riêng của tranh dân gian.</t>
-        </is>
-      </c>
+      <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -13117,7 +13105,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS khảo sát, tổng hợp được số liệu về cảnh quan trường lớp và chỉ ra việc cần làm.</t>
+          <t>Năng lực số 1.1 CB2c: HS khảo sát, tổng hợp được số liệu về cảnh quan trường lớp và chỉ ra việc cần làm.
+Học tập và làm theo Bác: Điều 4 “Giữ gìn vệ sinh thật tốt” (mạch 4): khi lập kế hoạch giữ trường học xanh, sạch, đẹp, mỗi tổ ghi rõ việc, người làm, thời gian; HS thực hiện ở tiết sinh hoạt lớp cuối tuần.</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13963,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -14004,7 +13993,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -14039,7 +14028,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -14074,7 +14063,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -14104,7 +14093,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -14139,7 +14128,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -14906,7 +14895,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -14940,7 +14929,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -14962,7 +14951,8 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí cảnh quan địa phương trên bản đồ số và mô tả đặc điểm của nó.</t>
+          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí cảnh quan địa phương trên bản đồ số và mô tả đặc điểm của nó.
+QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
     </row>
@@ -14974,7 +14964,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -14996,7 +14986,8 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
+          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.
+KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
     </row>
@@ -15008,7 +14999,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -15043,7 +15034,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -15078,7 +15069,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -15113,7 +15104,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -15148,7 +15139,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -15183,7 +15174,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -15218,7 +15209,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -15253,7 +15244,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -15288,7 +15279,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -16953,19 +16944,19 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Một số đơn vị đo đại lượng</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Yến, tạ, tấn (Tiết 1)</t>
+          <t>Kiểm tra định kì giữa học kì I</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -16973,11 +16964,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
-        </is>
-      </c>
+      <c r="H40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -16994,10 +16981,14 @@
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Yến, tạ, tấn (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr"/>
+          <t>Bài 17. Yến, tạ, tấn (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
           <t>38</t>
@@ -17024,7 +17015,7 @@
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Yến, tạ, tấn (Tiết 3)</t>
+          <t>Bài 17. Yến, tạ, tấn (Tiết 2)</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
@@ -17035,7 +17026,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.4 CB2a: HS tự soát lại bài bằng công cụ chấm nhanh của GV và chỉ ra dạng quy đổi mình còn hay nhầm.</t>
+          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
         </is>
       </c>
     </row>
@@ -17054,14 +17045,10 @@
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>4 tiết</t>
-        </is>
-      </c>
+          <t>Bài 17. Yến, tạ, tấn (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr">
         <is>
           <t>40</t>
@@ -17069,7 +17056,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
+          <t>Năng lực số 5.4 CB2a: HS tự soát lại bài bằng công cụ chấm nhanh của GV và chỉ ra dạng quy đổi mình còn hay nhầm.</t>
         </is>
       </c>
     </row>
@@ -17088,10 +17075,14 @@
       <c r="D44" s="4" t="inlineStr"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
+          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>4 tiết</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
           <t>41</t>
@@ -17118,7 +17109,7 @@
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 3)</t>
+          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 2)</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
@@ -17148,7 +17139,7 @@
       <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 4)</t>
+          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 3)</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
@@ -17178,14 +17169,10 @@
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Giây, thế kỉ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 18. Đề-xi-mét vuông, mét vuông, mi-li-mét vuông (Tiết 4)</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr">
         <is>
           <t>44</t>
@@ -17193,8 +17180,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.
-STEM: Thế kỉ (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
+          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
         </is>
       </c>
     </row>
@@ -17213,10 +17199,14 @@
       <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Giây, thế kỉ (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr"/>
+          <t>Bài 19. Giây, thế kỉ (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
           <t>45</t>
@@ -17224,7 +17214,8 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.</t>
+          <t>Năng lực số 1.1 CB2c: HS đo được đại lượng thật bằng dụng cụ đo và thiết bị số, ghi số liệu vào bảng chung.
+STEM: Thế kỉ (Toán – Mĩ thuật) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -17236,21 +17227,17 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 4: Một số đơn vị đo đại lượng</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì I</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 19. Giây, thế kỉ (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
       <c r="G49" s="4" t="inlineStr">
         <is>
           <t>46</t>
@@ -17601,11 +17588,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS nêu được các bước giải và nhận ra cấu trúc bài toán không đổi khi số liệu thay đổi.</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -17631,11 +17614,7 @@
           <t>58</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB2a: HS làm bài tập tương tác, tự xác định dạng bài mình còn yếu và luyện thêm.</t>
-        </is>
-      </c>
+      <c r="H61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -17918,11 +17897,7 @@
           <t>67</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
-        </is>
-      </c>
+      <c r="H70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -18047,11 +18022,7 @@
           <t>71</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
-        </is>
-      </c>
+      <c r="H74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -18359,11 +18330,7 @@
           <t>81</t>
         </is>
       </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
-        </is>
-      </c>
+      <c r="H84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -18389,11 +18356,7 @@
           <t>82</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
-        </is>
-      </c>
+      <c r="H85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -19160,11 +19123,7 @@
           <t>107</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS nêu được các bước giải và nhận ra cấu trúc bài toán không đổi khi số liệu thay đổi.</t>
-        </is>
-      </c>
+      <c r="H110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -19190,11 +19149,7 @@
           <t>108</t>
         </is>
       </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS nêu được các bước giải và nhận ra cấu trúc bài toán không đổi khi số liệu thay đổi.</t>
-        </is>
-      </c>
+      <c r="H111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -19992,11 +19947,7 @@
           <t>133</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS giải thích được khái niệm phân số và phân số bằng nhau nhờ quan sát mô hình động.</t>
-        </is>
-      </c>
+      <c r="H136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -20026,11 +19977,7 @@
           <t>134</t>
         </is>
       </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS giải thích được khái niệm phân số và phân số bằng nhau nhờ quan sát mô hình động.</t>
-        </is>
-      </c>
+      <c r="H137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -20389,11 +20336,7 @@
           <t>146</t>
         </is>
       </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB2a: HS làm bài tập tương tác, tự xác định dạng bài mình còn yếu và luyện thêm.</t>
-        </is>
-      </c>
+      <c r="H149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -20943,11 +20886,7 @@
           <t>164</t>
         </is>
       </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc, viết, so sánh, làm tròn được các số lớn lấy từ số liệu thật, có ghi nguồn.</t>
-        </is>
-      </c>
+      <c r="H167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -20973,11 +20912,7 @@
           <t>165</t>
         </is>
       </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc, viết, so sánh, làm tròn được các số lớn lấy từ số liệu thật, có ghi nguồn.</t>
-        </is>
-      </c>
+      <c r="H168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -21071,11 +21006,7 @@
           <t>168</t>
         </is>
       </c>
-      <c r="H171" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS giải thích được khái niệm phân số và phân số bằng nhau nhờ quan sát mô hình động.</t>
-        </is>
-      </c>
+      <c r="H171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -21681,7 +21612,7 @@
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Yêu lao động”, GV chiếu bộ ảnh người lao động ở nhiều nghề và ảnh HS làm việc vừa sức như trực nhật, tưới cây, gấp quần áo
 Năng lực số Miền 2 (Cơ bản, bậc 2): GV gõ lên màn hình những việc HS kể thành bảng hai cột việc ở nhà và việc ở trường; cả lớp cùng đọc
-KNS: KN chi tiêu và giữ gìn: dùng đồ dùng, tiền bạc hợp lí, giữ gìn của công.</t>
+Học tập và làm theo Bác: Điều 2 “Học tập tốt, lao động tốt” (mạch 2): khi kể tấm gương yêu lao động, HS nêu điều mình học được và tự nhận một việc lao động vừa sức, làm đều đặn trong tuần ở nhà hoặc ở lớp.</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22813,7 @@
       <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 1.2 CB2a: HS nêu được vì sao phải theo dõi bản tin mới nhất và không chia sẻ tin bão chưa kiểm chứng.
-STEM: Gió, bão (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
+STEM: Dụng cụ đo sức gió (Khoa học – Công nghệ – Toán) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -22912,7 +22843,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS nêu được vì sao phải theo dõi bản tin mới nhất và không chia sẻ tin bão chưa kiểm chứng.</t>
+          <t>Năng lực số 1.2 CB2a: HS nêu được vì sao phải theo dõi bản tin mới nhất và không chia sẻ tin bão chưa kiểm chứng.
+STEM: Dụng cụ đo sức gió (Khoa học – Công nghệ – Toán) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -23019,19 +22951,19 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập giữa học kì I</t>
+          <t>Bài 9. Vai trò của ánh sáng (Tiết 1)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -23039,7 +22971,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.1 CB2a: HS giải thích được sự tạo thành bóng và ánh sáng truyền theo đường thẳng nhờ mô phỏng và thí nghiệm.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -23049,27 +22985,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì I</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 9. Vai trò của ánh sáng (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.1 CB2a: HS giải thích được sự tạo thành bóng và ánh sáng truyền theo đường thẳng nhờ mô phỏng và thí nghiệm.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -23086,7 +23022,7 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Vai trò của ánh sáng (Tiết 1)</t>
+          <t>Bài 10. Âm thanh và sự truyền âm thanh (Tiết 1)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -23101,7 +23037,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.1 CB2a: HS giải thích được sự tạo thành bóng và ánh sáng truyền theo đường thẳng nhờ mô phỏng và thí nghiệm.</t>
+          <t>Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.</t>
         </is>
       </c>
     </row>
@@ -23120,7 +23056,7 @@
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Vai trò của ánh sáng (Tiết 2)</t>
+          <t>Bài 10. Âm thanh và sự truyền âm thanh (Tiết 2)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -23131,7 +23067,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.1 CB2a: HS giải thích được sự tạo thành bóng và ánh sáng truyền theo đường thẳng nhờ mô phỏng và thí nghiệm.</t>
+          <t>Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.</t>
         </is>
       </c>
     </row>
@@ -23150,7 +23086,7 @@
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Âm thanh và sự truyền âm thanh (Tiết 1)</t>
+          <t>Bài 11. Âm thanh trong cuộc sống (Tiết 1)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -23165,7 +23101,9 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.</t>
+          <t>NLS-ST: Tạo sản phẩm học tập số đơn giản (sơ đồ, áp phích) trình bày kết quả.
+Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.
+STEM: Âm thanh trong cuộc sống (Khoa học – Âm nhạc) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -23184,7 +23122,7 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Âm thanh và sự truyền âm thanh (Tiết 2)</t>
+          <t>Bài 11. Âm thanh trong cuộc sống (Tiết 2)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -23214,7 +23152,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Âm thanh trong cuộc sống (Tiết 1)</t>
+          <t>Bài 12. Nhiệt độ và sự truyền nhiệt (Tiết 1)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -23229,9 +23167,8 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST: Tạo sản phẩm học tập số đơn giản (sơ đồ, áp phích) trình bày kết quả.
-Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.
-STEM: Âm thanh trong cuộc sống (Khoa học – Âm nhạc) — dạy thay cho tiết này.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Nhiệt độ và sự truyền nhiệt”, GV chiếu ảnh phóng to mặt nhiệt kế để cả lớp cùng đọc đúng số chỉ
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả đo vào bảng chiếu trên màn hình rồi cùng đối chiếu; khi số liệu các nhóm khác nhau, cả lớp tìm nguyên nhân là đặt nhiệt kế gần cửa sổ</t>
         </is>
       </c>
     </row>
@@ -23250,7 +23187,7 @@
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Âm thanh trong cuộc sống (Tiết 2)</t>
+          <t>Bài 12. Nhiệt độ và sự truyền nhiệt (Tiết 2)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -23261,7 +23198,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.</t>
+          <t>Năng lực số 1.3 CB2a: HS ghi số đo nhiệt độ theo từng mốc thời gian vào bảng trên máy và tìm lại được số liệu của nhóm mình để so sánh.</t>
         </is>
       </c>
     </row>
@@ -23280,7 +23217,7 @@
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Bài 12. Nhiệt độ và sự truyền nhiệt (Tiết 1)</t>
+          <t>Bài 13. Vật dẫn nhiệt tốt, vật dẫn nhiệt kém (Tiết 1)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -23295,8 +23232,9 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Nhiệt độ và sự truyền nhiệt”, GV chiếu ảnh phóng to mặt nhiệt kế để cả lớp cùng đọc đúng số chỉ
-Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả đo vào bảng chiếu trên màn hình rồi cùng đối chiếu; khi số liệu các nhóm khác nhau, cả lớp tìm nguyên nhân là đặt nhiệt kế gần cửa sổ</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài vật dẫn nhiệt tốt và vật dẫn nhiệt kém, GV chiếu mô phỏng nhiệt truyền qua thìa kim loại và thìa gỗ cắm trong cốc nước nóng
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả thí nghiệm vào bảng chiếu trên màn hình rồi đối chiếu với dự đoán; khi kết quả các nhóm khác nhau
+STEM: Dẫn nhiệt (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -23315,7 +23253,7 @@
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bài 12. Nhiệt độ và sự truyền nhiệt (Tiết 2)</t>
+          <t>Bài 13. Vật dẫn nhiệt tốt, vật dẫn nhiệt kém (Tiết 2)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -23324,11 +23262,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.3 CB2a: HS ghi số đo nhiệt độ theo từng mốc thời gian vào bảng trên máy và tìm lại được số liệu của nhóm mình để so sánh.</t>
-        </is>
-      </c>
+      <c r="H28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -23345,12 +23279,12 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bài 13. Vật dẫn nhiệt tốt, vật dẫn nhiệt kém (Tiết 1)</t>
+          <t>Bài 14. Ôn tập chủ đề Năng lượng</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -23358,12 +23292,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài vật dẫn nhiệt tốt và vật dẫn nhiệt kém, GV chiếu mô phỏng nhiệt truyền qua thìa kim loại và thìa gỗ cắm trong cốc nước nóng
-Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả thí nghiệm vào bảng chiếu trên màn hình rồi đối chiếu với dự đoán; khi kết quả các nhóm khác nhau</t>
-        </is>
-      </c>
+      <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -23373,23 +23302,31 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: Năng lượng</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bài 13. Vật dẫn nhiệt tốt, vật dẫn nhiệt kém (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>Bài 15. Thực vật cần gì để sống? (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.3 CB2a: HS ghi, đọc được bảng theo dõi và chuỗi ảnh để rút ra kết luận từ số liệu của chính mình.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -23399,27 +23336,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: Năng lượng</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bài 14. Ôn tập chủ đề Năng lượng</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 15. Thực vật cần gì để sống? (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.3 CB2a: HS ghi, đọc được bảng theo dõi và chuỗi ảnh để rút ra kết luận từ số liệu của chính mình.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -23436,14 +23373,10 @@
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bài 15. Thực vật cần gì để sống? (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 15. Thực vật cần gì để sống? (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
           <t>29</t>
@@ -23470,10 +23403,14 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bài 15. Thực vật cần gì để sống? (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>Bài 16. Động vật cần gì để sống? (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
           <t>30</t>
@@ -23500,7 +23437,7 @@
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bài 15. Thực vật cần gì để sống? (Tiết 3)</t>
+          <t>Bài 16. Động vật cần gì để sống? (Tiết 2)</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -23530,14 +23467,10 @@
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Bài 16. Động vật cần gì để sống? (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 16. Động vật cần gì để sống? (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
           <t>32</t>
@@ -23564,10 +23497,14 @@
       <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Bài 16. Động vật cần gì để sống? (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
+          <t>Bài 17. Chăm sóc cây trồng, vật nuôi (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
           <t>33</t>
@@ -23594,7 +23531,7 @@
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Bài 16. Động vật cần gì để sống? (Tiết 3)</t>
+          <t>Bài 17. Chăm sóc cây trồng, vật nuôi (Tiết 2)</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -23605,7 +23542,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS ghi, đọc được bảng theo dõi và chuỗi ảnh để rút ra kết luận từ số liệu của chính mình.</t>
+          <t>Năng lực số 1.3 CB2a: HS ghi bảng theo dõi việc chăm sóc vật nuôi ở nhà trong một tuần (ngày, việc đã làm, biểu hiện của con vật) và đọc lại bảng để rút ra nhận xét.</t>
         </is>
       </c>
     </row>
@@ -23617,14 +23554,14 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
       <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập cuối học kì I</t>
+          <t>Bài 18. Ôn tập chủ đề Thực vật và động vật</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -23677,14 +23614,14 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Thực vật và động vật</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Chăm sóc cây trồng, vật nuôi (Tiết 1)</t>
+          <t>Bài 19. Đặc điểm chung của nấm (Tiết 1)</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -23699,7 +23636,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS ghi, đọc được bảng theo dõi và chuỗi ảnh để rút ra kết luận từ số liệu của chính mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
         </is>
       </c>
     </row>
@@ -23711,14 +23648,14 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Thực vật và động vật</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Chăm sóc cây trồng, vật nuôi (Tiết 2)</t>
+          <t>Bài 19. Đặc điểm chung của nấm (Tiết 2)</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
@@ -23729,7 +23666,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS ghi bảng theo dõi việc chăm sóc vật nuôi ở nhà trong một tuần (ngày, việc đã làm, biểu hiện của con vật) và đọc lại bảng để rút ra nhận xét.</t>
+          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
         </is>
       </c>
     </row>
@@ -23741,19 +23678,19 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Thực vật và động vật</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Ôn tập chủ đề Thực vật và động vật</t>
+          <t>Bài 20. Nấm ăn và nấm trong chế biến thực phẩm (Tiết 1)</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -23761,7 +23698,11 @@
           <t>39</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -23778,14 +23719,10 @@
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Đặc điểm chung của nấm (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 20. Nấm ăn và nấm trong chế biến thực phẩm (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr">
         <is>
           <t>40</t>
@@ -23812,10 +23749,14 @@
       <c r="D44" s="4" t="inlineStr"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Đặc điểm chung của nấm (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
+          <t>Bài 21. Nấm gây hỏng thực phẩm và nấm độc (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
           <t>41</t>
@@ -23842,14 +23783,10 @@
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Bài 20. Nấm ăn và nấm trong chế biến thực phẩm (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 21. Nấm gây hỏng thực phẩm và nấm độc (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr">
         <is>
           <t>42</t>
@@ -23876,20 +23813,20 @@
       <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Bài 20. Nấm ăn và nấm trong chế biến thực phẩm (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
+          <t>Bài 22. Ôn tập chủ đề Nấm</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
-        </is>
-      </c>
+      <c r="H46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -23899,14 +23836,14 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Nấm</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Bài 21. Nấm gây hỏng thực phẩm và nấm độc (Tiết 1)</t>
+          <t>Bài 23. Vai trò của chất dinh dưỡng đối với cơ thể (Tiết 1)</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -23921,7 +23858,8 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
         </is>
       </c>
     </row>
@@ -23933,14 +23871,14 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Nấm</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
       <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Bài 21. Nấm gây hỏng thực phẩm và nấm độc (Tiết 2)</t>
+          <t>Bài 23. Vai trò của chất dinh dưỡng đối với cơ thể (Tiết 2)</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -23951,7 +23889,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
         </is>
       </c>
     </row>
@@ -23963,19 +23901,19 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Nấm</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Ôn tập chủ đề Nấm</t>
+          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 1)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -23983,102 +23921,7 @@
           <t>46</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Bài 23. Vai trò của chất dinh dưỡng đối với cơ thể (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Bài 23. Vai trò của chất dinh dưỡng đối với cơ thể (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>NLS-ST: Tạo sản phẩm học tập số đơn giản (sơ đồ, áp phích) trình bày kết quả.
 Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
@@ -24087,6 +23930,101 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
@@ -24102,7 +24040,7 @@
       <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 2)</t>
+          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 2)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
@@ -24132,7 +24070,7 @@
       <c r="D54" s="4" t="inlineStr"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 3)</t>
+          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 3)</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
@@ -24162,12 +24100,12 @@
       <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 1)</t>
+          <t>Bài 26. Thực phẩm an toàn (Tiết 1)</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -24177,8 +24115,8 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+          <t>Năng lực số 5.1 CB2a: HS nêu được cách xử lí khi gặp thực phẩm hết hạn, bao bì hỏng hoặc không rõ nguồn gốc.
+KNS: KN an toàn khi thực hành: làm đúng hướng dẫn, không tự ý thử nghiệm nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -24197,7 +24135,7 @@
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 2)</t>
+          <t>Bài 26. Thực phẩm an toàn (Tiết 2)</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
@@ -24208,7 +24146,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
+          <t>Năng lực số 5.1 CB2a: HS nêu được cách xử lí khi gặp thực phẩm hết hạn, bao bì hỏng hoặc không rõ nguồn gốc.</t>
         </is>
       </c>
     </row>
@@ -24227,10 +24165,14 @@
       <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
+          <t>Bài 27. Phòng tránh đuối nước (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
           <t>54</t>
@@ -24238,7 +24180,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS nêu và làm được các bước cứu người đuối nước an toàn từ trên bờ.</t>
         </is>
       </c>
     </row>
@@ -24250,27 +24192,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì II</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 27. Phòng tránh đuối nước (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB2c: HS nêu và làm được các bước cứu người đuối nước an toàn từ trên bờ.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -24287,7 +24229,7 @@
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Thực phẩm an toàn (Tiết 1)</t>
+          <t>Bài 28. Ôn tập chủ đề Con người và sức khoẻ (Tiết 1)</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -24300,12 +24242,7 @@
           <t>56</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.1 CB2a: HS nêu được cách xử lí khi gặp thực phẩm hết hạn, bao bì hỏng hoặc không rõ nguồn gốc.
-KNS: KN an toàn khi thực hành: làm đúng hướng dẫn, không tự ý thử nghiệm nguy hiểm.</t>
-        </is>
-      </c>
+      <c r="H59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -24322,7 +24259,7 @@
       <c r="D60" s="4" t="inlineStr"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Thực phẩm an toàn (Tiết 2)</t>
+          <t>Bài 28. Ôn tập chủ đề Con người và sức khoẻ (Tiết 2)</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
@@ -24331,11 +24268,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.1 CB2a: HS nêu được cách xử lí khi gặp thực phẩm hết hạn, bao bì hỏng hoặc không rõ nguồn gốc.</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -24345,19 +24278,19 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bài 27. Phòng tránh đuối nước (Tiết 1)</t>
+          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 1)</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -24367,7 +24300,9 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu và làm được các bước cứu người đuối nước an toàn từ trên bờ.</t>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.
+STEM: Chuỗi thức ăn trong tự nhiên (Khoa học – Mĩ thuật) — dạy thay cho tiết này.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
         </is>
       </c>
     </row>
@@ -24379,14 +24314,14 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
       <c r="D62" s="4" t="inlineStr"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bài 27. Phòng tránh đuối nước (Tiết 2)</t>
+          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 2)</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -24397,7 +24332,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu và làm được các bước cứu người đuối nước an toàn từ trên bờ.</t>
+          <t>Năng lực số 2.5 CB2a: HS trình chiếu sơ đồ của nhóm và góp ý cho nhóm bạn một cách lịch sự, đúng mực.</t>
         </is>
       </c>
     </row>
@@ -24409,27 +24344,27 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Bài 28. Ôn tập chủ đề Con người và sức khoẻ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -24439,23 +24374,32 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
       <c r="D64" s="4" t="inlineStr"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bài 28. Ôn tập chủ đề Con người và sức khoẻ (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
+          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -24472,14 +24416,10 @@
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="inlineStr">
         <is>
           <t>62</t>
@@ -24487,9 +24427,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.
-STEM: Chuỗi thức ăn trong tự nhiên (Khoa học – Mĩ thuật) — dạy thay cho tiết này.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
         </is>
       </c>
     </row>
@@ -24508,7 +24446,7 @@
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 2)</t>
+          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 3)</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -24519,7 +24457,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB2a: HS trình chiếu sơ đồ của nhóm và góp ý cho nhóm bạn một cách lịch sự, đúng mực.</t>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
         </is>
       </c>
     </row>
@@ -24538,20 +24476,20 @@
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
+          <t>Bài 31. Ôn tập chủ đề Sinh vật và môi trường</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
-        </is>
-      </c>
+      <c r="H67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -24561,19 +24499,19 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
       <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 1)</t>
+          <t>Ôn tập cuối năm (Tiết 1)</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -24581,12 +24519,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
-        </is>
-      </c>
+      <c r="H68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -24596,27 +24529,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
+          <t>Ôn tập cuối năm (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
-        </is>
-      </c>
+      <c r="H69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -24626,27 +24559,27 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
       <c r="D70" s="4" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr"/>
+          <t>Ôn tập cuối năm (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
-        </is>
-      </c>
+      <c r="H70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -24656,14 +24589,14 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bài 31. Ôn tập chủ đề Sinh vật và môi trường</t>
+          <t>Ôn tập cuối năm (Tiết 4)</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -24693,7 +24626,7 @@
       <c r="D72" s="4" t="inlineStr"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập cuối năm học</t>
+          <t>Kiểm tra định kì cuối năm học</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -24716,14 +24649,14 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Tiết dự phòng theo SGV</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì cuối năm học</t>
+          <t>Tiết dự phòng (nhà trường tự bố trí)</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -24736,7 +24669,11 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>SGV không xếp bài cho tiết này</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -24852,7 +24789,8 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được ảnh tư liệu gốc với hình minh hoạ do máy tạo và biết ghi nguồn tư liệu.</t>
+          <t>Tích hợp QPAN: khai thác bản đồ Việt Nam, lược đồ khởi nghĩa Hai Bà Trưng để bồi dưỡng lòng yêu nước, tự hào dân tộc, ý thức bảo vệ chủ quyền, toàn vẹn lãnh thổ.
+Tích hợp NLS 1.1.CB2a, 4.2.CB2b: HS quan sát bản đồ số/hình ảnh số/bảng số liệu GV trình chiếu; xác định được thông tin cần tìm; không nhập thông tin cá nhân khi sử dụng học liệu số.</t>
         </is>
       </c>
     </row>
@@ -24882,7 +24820,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được ảnh tư liệu gốc với hình minh hoạ do máy tạo và biết ghi nguồn tư liệu.</t>
+          <t>Gợi ý vận dụng AI (không làm tăng YCCĐ) – 4.A1.2 (QĐ 2422): GV dùng công cụ AI để chuẩn bị khung sơ đồ tư duy, câu hỏi gợi ý và phiếu phân hoá, kiểm duyệt trước khi in/chiếu; HS không trực tiếp dùng AI, chỉ dùng phiếu gợi ý trên giấy để tự hoàn thiện sản phẩm.</t>
         </is>
       </c>
     </row>
@@ -24916,7 +24854,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí và đặc điểm nổi bật của địa phương mình trên bản đồ số, ảnh vệ tinh.
+          <t>Tích hợp BVMT: HS nhận biết quyền được sống trong môi trường an toàn, trong lành; biết yêu quý, bảo vệ cảnh quan địa phương.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -24947,7 +24885,8 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí và đặc điểm nổi bật của địa phương mình trên bản đồ số, ảnh vệ tinh.</t>
+          <t>Gợi ý vận dụng AI (không làm tăng YCCĐ) – 4.A1.1 (QĐ 2422): HS nhận diện được cách AI có thể hỗ trợ các hoạt động kinh tế như nông nghiệp, dịch vụ, du lịch ở địa phương; biết thông tin do AI gợi ý cần được kiểm chứng.
+Tích hợp NLS 1.2.CB2a, 2.2.CB2b: HS tìm thông tin cơ bản về địa phương từ nguồn GV giới thiệu, chọn lọc thông tin đáng tin cậy và ghi nguồn khi giới thiệu địa danh.</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24920,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí và đặc điểm nổi bật của địa phương mình trên bản đồ số, ảnh vệ tinh.
+          <t>Tích hợp lý tưởng cách mạng, đạo đức, lối sống: HS tự hào, biết ơn các thế hệ đi trước; có ý thức giữ gìn truyền thống tốt đẹp của địa phương bằng lời nói, việc làm phù hợp với lứa tuổi.
 KNS: KN tôn trọng sự khác biệt về văn hoá, phong tục giữa các vùng miền, dân tộc.</t>
         </is>
       </c>
@@ -25012,7 +24951,8 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí và đặc điểm nổi bật của địa phương mình trên bản đồ số, ảnh vệ tinh.</t>
+          <t>Tích hợp QPAN: Giáo dục tinh thần yêu nước, ý thức trách nhiệm bảo vệ Tổ quốc trong thời đại hôm nay; biết ơn các thế hệ cha ông đã góp phần xây dựng và bảo vệ quê hương.
+Tích hợp NLS 3.1.CB2a, 5.2.CB2b: HS trình bày ngắn gọn một di tích, lễ hội hoặc nhân vật địa phương bằng tranh, sơ đồ; nhận ra công cụ số (trang trình chiếu do GV thao tác) có thể giúp trình bày rõ hơn.</t>
         </is>
       </c>
     </row>
@@ -25046,7 +24986,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.
+          <t>Tích hợp QPAN: HS nhận biết vị trí vùng biên giới phía Bắc; hình thành ý thức yêu quê hương, tôn trọng cột mốc, đường biên, chủ quyền lãnh thổ.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -25077,7 +25017,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.</t>
+          <t>Tích hợp BVMT: HS biết vai trò của rừng đầu nguồn, nguồn nước; có ý thức phòng tránh thiên tai, bảo vệ cảnh quan miền núi.</t>
         </is>
       </c>
     </row>
@@ -25107,7 +25047,8 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.</t>
+          <t>Tích hợp NLS 1.1.CB2c: HS quan sát lược đồ/bản đồ số do GV cung cấp, biết cách xem (phóng to, di chuyển) để đọc tên bản đồ, xem chú giải, xác định vị trí, địa hình, sông ngòi của vùng; biết đối chiếu với SGK, dùng nguồn an toàn và không nhập thông tin cá nhân.
+Tích hợp tiết kiệm và bảo vệ nguồn nước: HS liên hệ một số việc làm bảo vệ thiên nhiên, sử dụng nước hợp lí và phòng, chống thiên tai.</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25082,8 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS lập bảng và đọc được biểu đồ dân cư, từ đó giải thích sự phân bố dân cư của vùng.
+          <t>Tích hợp QCN: HS tôn trọng sự đa dạng dân tộc, bình đẳng giữa các cộng đồng; không kì thị phong tục, trang phục, tiếng nói của các dân tộc.
+Gợi ý vận dụng AI (không làm tăng YCCĐ) – 4.C2.1 (QĐ 2422): HS hiểu AI có thể hỗ trợ thống kê, sắp xếp, tạo bảng/biểu đồ và gợi ý nhận xét dữ liệu dân cư; biết kiểm chứng với SGK, lược đồ, nguồn chính thống, không sao chép máy móc và không nhập thông tin cá nhân.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -25172,7 +25114,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS lập bảng và đọc được biểu đồ dân cư, từ đó giải thích sự phân bố dân cư của vùng.</t>
+          <t>Tích hợp tiết kiệm và bảo vệ nguồn nước: HS hiểu sản xuất nông nghiệp, thủy điện, khai thác khoáng sản cần gắn với bảo vệ rừng, đất, nước; biết sử dụng nước hợp lí và không làm ô nhiễm nguồn nước.</t>
         </is>
       </c>
     </row>
@@ -25202,7 +25144,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS lập bảng và đọc được biểu đồ dân cư, từ đó giải thích sự phân bố dân cư của vùng.</t>
+          <t>Tích hợp NLS 1.2.CB2a, 2.2.CB2b: HS chọn hình ảnh/thông tin về dân tộc, hoạt động sản xuất từ nguồn GV giới thiệu; nhận biết nguồn đáng tin cậy, chọn lọc thông tin đúng trọng tâm và ghi nguồn hình ảnh đã dùng.
+Gợi ý vận dụng AI (không làm tăng YCCĐ) – 4.A1.2 (QĐ 2422): GV dùng công cụ AI soạn trước bộ câu hỏi tự kiểm tra, kiểm duyệt rồi in/chiếu; HS không trực tiếp dùng AI, chỉ dùng câu hỏi trên giấy để rà soát và tự chỉnh sửa phần chia sẻ.</t>
         </is>
       </c>
     </row>
@@ -25236,8 +25179,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Nội dung giáo dục địa phương — đối chiếu tài liệu GDĐP của tỉnh.
-Năng lực số 1.1 CB2c: HS mô tả được nét đặc sắc của lễ hội, nét văn hoá vùng miền nhờ phim tư liệu chính thống.
+          <t>Tích hợp QCN: HS biết tôn trọng quyền giữ gìn bản sắc văn hoá của các dân tộc; ứng xử văn minh khi quan sát, giới thiệu lễ hội, làn điệu dân ca, trang phục và phong tục của các dân tộc.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -25268,7 +25210,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được nét đặc sắc của lễ hội, nét văn hoá vùng miền nhờ phim tư liệu chính thống.</t>
+          <t>Tích hợp NLS 1.2.CB2a, 4.2.CB2b: HS xem hình ảnh/video văn hoá từ nguồn GV cung cấp; biết chọn lọc thông tin phù hợp, không chia sẻ thông tin cá nhân hoặc hình ảnh người khác lên môi trường số khi chưa được phép.</t>
         </is>
       </c>
     </row>
@@ -25302,7 +25244,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được nét đặc sắc của lễ hội, nét văn hoá vùng miền nhờ phim tư liệu chính thống.
+          <t>Tích hợp lý tưởng cách mạng, đạo đức, lối sống: HS bồi dưỡng lòng biết ơn cội nguồn, tự hào truyền thống dựng nước và giữ nước; có ý thức học tập, giữ gìn và giới thiệu đúng về di tích Đền Hùng, lễ giỗ Tổ Hùng Vương.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -25333,7 +25275,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được nét đặc sắc của lễ hội, nét văn hoá vùng miền nhờ phim tư liệu chính thống.</t>
+          <t>Tích hợp NLS 1.1.CB2a, 1.1.CB2b: HS xác định được thông tin cần tìm về truyền thuyết thời Hùng Vương; cùng GV tìm kiếm đơn giản từ nguồn GV giới thiệu, chọn lọc thông tin phù hợp, không sao chép máy móc.</t>
         </is>
       </c>
     </row>
@@ -25345,19 +25287,19 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 3: Đồng bằng Bắc Bộ</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì I</t>
+          <t>Bài 8. Thiên nhiên vùng Đồng bằng Bắc Bộ (Tiết 1)</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -25365,7 +25307,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp BVMT: HS nhận biết vẻ đẹp, vai trò của thiên nhiên vùng Đồng bằng Bắc Bộ; có thái độ yêu quý sông ngòi, đất phù sa, sinh vật và cảnh quan tự nhiên.
+QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -25382,14 +25329,10 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Bài 8. Thiên nhiên vùng Đồng bằng Bắc Bộ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 8. Thiên nhiên vùng Đồng bằng Bắc Bộ (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>18</t>
@@ -25397,8 +25340,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.
-QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+          <t>Tích hợp tiết kiệm và bảo vệ nguồn nước: HS biết vai trò của hệ thống sông ngòi, hồ đầm, kênh rạch; có ý thức tiết kiệm nước, không xả rác, bảo vệ nguồn nước trong sinh hoạt và sản xuất.</t>
         </is>
       </c>
     </row>
@@ -25417,7 +25359,7 @@
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bài 8. Thiên nhiên vùng Đồng bằng Bắc Bộ (Tiết 2)</t>
+          <t>Bài 8. Thiên nhiên vùng Đồng bằng Bắc Bộ (Tiết 3)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -25428,7 +25370,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.</t>
+          <t>Tích hợp NLS 1.1.CB2a, 1.1.CB2b: HS xác định được thông tin cần tìm về một con sông ở vùng Đồng bằng Bắc Bộ; tìm kiếm đơn giản từ nguồn GV giới thiệu (tại lớp qua máy GV, ở nhà cùng người lớn), chọn lọc ý chính, không sao chép máy móc.</t>
         </is>
       </c>
     </row>
@@ -25447,10 +25389,14 @@
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bài 8. Thiên nhiên vùng Đồng bằng Bắc Bộ (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
+          <t>Bài 9. Dân cư và hoạt động sản xuất ở vùng Đồng bằng Bắc Bộ (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>20</t>
@@ -25458,7 +25404,8 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.</t>
+          <t>Tích hợp NLS 1.1.CB2c, 1.2.CB2a: HS bước đầu biết xác định thông tin cần tìm khi xem lược đồ/bản đồ số về dân cư; biết quan sát chú giải, năm số liệu, chọn lọc thông tin phù hợp và không kết luận vội khi chưa đối chiếu với SGK.
+QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
     </row>
@@ -25477,14 +25424,10 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Dân cư và hoạt động sản xuất ở vùng Đồng bằng Bắc Bộ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 9. Dân cư và hoạt động sản xuất ở vùng Đồng bằng Bắc Bộ (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>21</t>
@@ -25492,10 +25435,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Bổ sung bài còn thiếu theo mục lục SGK (Tổ CM đối chiếu SGK)
-Năng lực số Miền 1 (Cơ bản, bậc 2): HS tra số liệu dân số, mật độ dân cư của vùng trong bài “Dân cư và hoạt động sản xuất ở vùng đồng bằng Bắc Bộ” từ nguồn chính thống
-Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu phim ngắn về hoạt động sản xuất tiêu biểu của vùng (trồng chè, khai thác khoáng sản, đánh bắt và nuôi trồng thuỷ sản, làm muối)
-QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+          <t>Tích hợp NLS 1.1.CB2b, 1.2.CB2a, 2.2.CB2b: HS quan sát GV tìm kiếm hình ảnh/video về nghề thủ công truyền thống từ nguồn đáng tin cậy; biết chọn lọc thông tin, ghi nguồn và không chia sẻ nội dung sai sự thật.</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25454,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Dân cư và hoạt động sản xuất ở vùng Đồng bằng Bắc Bộ (Tiết 2)</t>
+          <t>Bài 9. Dân cư và hoạt động sản xuất ở vùng Đồng bằng Bắc Bộ (Tiết 3)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -25523,7 +25463,11 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp NLS 1.1.CB2a, 1.2.CB2a, 2.2.CB2b: HS biết xác định thông tin cần tìm khi sưu tầm hình ảnh sản phẩm thủ công truyền thống; chọn nguồn đáng tin cậy, ghi nguồn, tóm tắt bằng lời của mình và chia sẻ an toàn, có trách nhiệm.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -25540,16 +25484,25 @@
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Dân cư và hoạt động sản xuất ở vùng Đồng bằng Bắc Bộ (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+          <t>Bài 10. Một số nét văn hoá ở vùng Đồng bằng Bắc Bộ (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp QCN: HS tôn trọng quyền tham gia, thụ hưởng đời sống văn hoá; biết ứng xử văn minh, tôn trọng không gian văn hoá chung và không chen lấn, xả rác khi tham gia lễ hội.
+QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -25566,14 +25519,10 @@
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Một số nét văn hoá ở vùng Đồng bằng Bắc Bộ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 10. Một số nét văn hoá ở vùng Đồng bằng Bắc Bộ (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
           <t>24</t>
@@ -25581,9 +25530,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu phim tư liệu về “Một số nét văn hóa ở vùng đồng bằng Bắc Bộ” do đài truyền hình, cơ quan văn hoá công bố: phần lễ, phần hội, trang phục
-Năng lực số Miền 3 (Cơ bản, bậc 2): HS làm một sản phẩm số nhỏ giới thiệu lễ hội hoặc nét văn hoá vừa học: trang chiếu có ảnh và chú thích, hoặc đoạn thuyết minh ghi âm
-QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+          <t>Tích hợp NLS 3.1.CB2a: HS tạo thẻ thông tin/tranh giới thiệu một nét văn hoá vùng Đồng bằng Bắc Bộ theo mẫu GV hướng dẫn; biết chọn hình ảnh, sắp xếp thông tin đơn giản, ghi nguồn và trình bày rõ ràng.</t>
         </is>
       </c>
     </row>
@@ -25602,10 +25549,14 @@
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Một số nét văn hoá ở vùng Đồng bằng Bắc Bộ (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>Bài 11. Sông Hồng và văn minh sông Hồng (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>25</t>
@@ -25613,7 +25564,9 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được nét đặc sắc của lễ hội, nét văn hoá vùng miền nhờ phim tư liệu chính thống.</t>
+          <t>Tích hợp tiết kiệm và bảo vệ nguồn nước: HS nhận biết vai trò của sông Hồng đối với đời sống, sản xuất; biết sử dụng nước tiết kiệm, không xả rác, không đổ chất thải xuống sông, kênh rạch.
+Gợi ý vận dụng AI (không làm tăng YCCĐ) – 4.A1.2 (QĐ 2422): GV dùng công cụ AI tạo một số tranh gợi ý về đời sống người Việt cổ qua hoa văn trống đồng và trình chiếu; HS quan sát, đối chiếu với hình trong SGK, nhận xét chi tiết đúng/chưa đúng và vẽ lại, chỉnh sửa trên giấy (HS không tự sử dụng công cụ AI).
+QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
     </row>
@@ -25632,14 +25585,10 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Sông Hồng và văn minh sông Hồng (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 11. Sông Hồng và văn minh sông Hồng (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr">
         <is>
           <t>26</t>
@@ -25647,8 +25596,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.
-QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+          <t>Tích hợp lý tưởng cách mạng, đạo đức, lối sống: HS tự hào về văn minh sông Hồng, trân trọng lao động của người Việt cổ; biết giữ gìn phong tục tốt đẹp, sống có trách nhiệm với cội nguồn và cộng đồng.</t>
         </is>
       </c>
     </row>
@@ -25667,10 +25615,14 @@
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Sông Hồng và văn minh sông Hồng (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>Bài 12. Thăng Long – Hà Nội (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
           <t>27</t>
@@ -25678,7 +25630,8 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.</t>
+          <t>Tích hợp lý tưởng cách mạng: HS nhận biết Hà Nội là Thủ đô, trung tâm chính trị - văn hoá; bồi dưỡng tình yêu Tổ quốc, niềm tự hào về truyền thống lịch sử của dân tộc.
+QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
         </is>
       </c>
     </row>
@@ -25697,14 +25650,10 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bài 12. Thăng Long – Hà Nội (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 12. Thăng Long – Hà Nội (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr">
         <is>
           <t>28</t>
@@ -25712,8 +25661,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.
-QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
+          <t>Tích hợp NLS 1.2.CB2a, 2.2.CB2b: HS chọn tư liệu đơn giản về Thăng Long – Hà Nội từ nguồn tin cậy, ghi tên nguồn; biết chọn lọc thông tin phù hợp và không sao chép máy móc.</t>
         </is>
       </c>
     </row>
@@ -25732,7 +25680,7 @@
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bài 12. Thăng Long – Hà Nội (Tiết 2)</t>
+          <t>Bài 12. Thăng Long – Hà Nội (Tiết 3)</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -25743,7 +25691,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.</t>
+          <t>Tích hợp QPAN: HS hiểu Hà Nội là Thủ đô, trung tâm chính trị quan trọng của đất nước; biết trân trọng các sự kiện lịch sử, giữ gìn di tích, công trình công cộng và có ý thức góp phần bảo vệ Thủ đô.</t>
         </is>
       </c>
     </row>
@@ -25762,10 +25710,14 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bài 12. Thăng Long – Hà Nội (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>Bài 13. Văn Miếu – Quốc Tử Giám (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
           <t>30</t>
@@ -25773,7 +25725,8 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.</t>
+          <t>Tích hợp lý tưởng cách mạng, đạo đức, lối sống: HS hình thành tinh thần hiếu học, kính trọng thầy cô, trân trọng truyền thống tôn sư trọng đạo.
+Gợi ý vận dụng AI (không làm tăng YCCĐ) – 4.A2.2 (QĐ 2422): HS nêu ý tưởng (bằng lời, trên giấy) về ứng dụng AI như trợ lý ảo hỗ trợ người khiếm thị hoặc khách tham quan tìm hiểu lịch sử tại Văn Miếu - Quốc Tử Giám.</t>
         </is>
       </c>
     </row>
@@ -25792,14 +25745,10 @@
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bài 13. Văn Miếu – Quốc Tử Giám (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 13. Văn Miếu – Quốc Tử Giám (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
       <c r="G34" s="4" t="inlineStr">
         <is>
           <t>31</t>
@@ -25807,7 +25756,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.</t>
+          <t>Tích hợp NLS 3.1.CB2a, 5.2.CB2b: HS trình bày sơ đồ/phiếu giới thiệu di tích trên giấy; nhận ra công cụ số (trang trình chiếu do GV thao tác) giúp chia sẻ sản phẩm rõ ràng hơn.</t>
         </is>
       </c>
     </row>
@@ -25826,10 +25775,14 @@
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Bài 13. Văn Miếu – Quốc Tử Giám (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr"/>
+          <t>Bài 14. Ôn tập</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
           <t>32</t>
@@ -25837,7 +25790,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.</t>
+          <t>Tích hợp NLS 2.1.CB2a: GV dùng Quizizz/Google Forms (câu hỏi có thể do AI gợi ý, GV đã kiểm duyệt) ở chế độ trình chiếu trên máy của lớp; HS trả lời, xem phản hồi đúng/sai, tự nhận xét mức độ nắm bài (HS không tự đăng nhập tài khoản).</t>
         </is>
       </c>
     </row>
@@ -25849,14 +25802,14 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Đồng bằng Bắc Bộ</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
       <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Bài 14. Ôn tập</t>
+          <t>Kiểm tra định kì cuối học kì I</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -25886,7 +25839,7 @@
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì cuối học kì I</t>
+          <t>Nhận xét, chữa bài kiểm tra định kì cuối học kì I</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -25931,7 +25884,8 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.
+          <t>Tích hợp QPAN: HS xác định vị trí vùng ven biển, quần đảo Hoàng Sa, Trường Sa; bồi dưỡng ý thức chủ quyền biển, đảo Việt Nam.
+Tích hợp AI (4.C2.1): HS hiểu được lòng cảm thông cần đi đôi với công nghệ: AI giúp dự báo chính xác, góp phần giảm thiệt hại cho đồng bào miền Trung.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -25962,7 +25916,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.</t>
+          <t>Tích hợp tiết kiệm và bảo vệ nguồn nước: HS nhận biết tác động của mưa, bão, hạn hán đến nguồn nước; biết sử dụng nước tiết kiệm, không làm ô nhiễm nguồn nước và thực hiện việc làm phù hợp để bảo vệ nguồn nước.</t>
         </is>
       </c>
     </row>
@@ -25992,7 +25946,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.</t>
+          <t>Tích hợp NLS 1.1.CB2a: HS đọc bản đồ/lược đồ để xác định sông ngòi, đất, rừng, biển đảo của vùng.</t>
         </is>
       </c>
     </row>
@@ -26020,7 +25974,11 @@
           <t>38</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp tiết kiệm và bảo vệ nguồn nước: HS nêu việc làm giữ gìn rừng, nguồn nước, bờ biển; không khai thác tài nguyên bừa bãi; biết bảo vệ nguồn nước trước tác động của bão, lũ, hạn hán.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -26046,7 +26004,11 @@
           <t>39</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp QPAN: HS nhận biết phòng, chống thiên tai góp phần bảo vệ đời sống nhân dân; biết chấp hành hướng dẫn của người lớn, lực lượng chức năng và chia sẻ phù hợp với đồng bào vùng bão lũ.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -26072,7 +26034,11 @@
           <t>40</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp NLS 1.2.CB2a: GV dùng hình ảnh/video/AI mô phỏng thiên tai đã kiểm duyệt; HS phân biệt thông tin đáng tin cậy và thông tin cần kiểm chứng.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -26104,7 +26070,7 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS lập bảng và đọc được biểu đồ dân cư, từ đó giải thích sự phân bố dân cư của vùng.
+          <t>Tích hợp QCN: HS tôn trọng sự đa dạng cộng đồng dân cư, biết đoàn kết và không phân biệt vùng miền.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -26135,7 +26101,8 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS lập bảng và đọc được biểu đồ dân cư, từ đó giải thích sự phân bố dân cư của vùng.</t>
+          <t>Tích hợp QPAN: HS hiểu hoạt động biển gắn với ý thức bảo vệ chủ quyền, chấp hành quy định của địa phương và lực lượng chức năng.
+Tích hợp ATGT: HS biết tuân thủ quy định an toàn khi tham gia giao thông đường biển, đường thủy.</t>
         </is>
       </c>
     </row>
@@ -26165,7 +26132,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS lập bảng và đọc được biểu đồ dân cư, từ đó giải thích sự phân bố dân cư của vùng.</t>
+          <t>Tích hợp NLS 1.1.CB2a, 3.1.CB2a: HS tìm thông tin du lịch/kinh tế biển từ nguồn GV cung cấp, trình bày bằng bảng hoặc sơ đồ đơn giản.</t>
         </is>
       </c>
     </row>
@@ -26193,7 +26160,11 @@
           <t>44</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp BVMT: HS hiểu sản xuất nông nghiệp, công nghiệp, thuỷ điện cần gắn với bảo vệ tài nguyên, môi trường và sinh kế bền vững.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -26255,7 +26226,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS lập bảng và đọc được biểu đồ dân cư, từ đó giải thích sự phân bố dân cư của vùng.
+          <t>Tích hợp NLS (1.1.CB2a): tìm kiếm, lựa chọn và kiểm chứng thông tin số về di sản theo nguồn do GV hướng dẫn.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -26286,8 +26257,8 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Tìm hiểu vùng đất hội tụ nhiều di sản của bài “Một số nét văn hoá ở vùng Bắc Trung Bộ và Nam Trung Bộ”
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động nhóm, GV chiếu bảng chung “Di sản – Nơi có – Nét đặc sắc”; các nhóm lên điền rồi đọc bảng của nhau</t>
+          <t>Tích hợp QPAN: giáo dục ý thức trân trọng công lao đội Hoàng Sa, trách nhiệm bảo vệ chủ quyền biển đảo qua Lễ Khao lề thế lính Hoàng Sa.
+Tích hợp tiết kiệm và bảo vệ nguồn nước: liên hệ hành vi văn minh, không xả rác, dùng nước tiết kiệm khi tham gia lễ hội gắn với biển, sông, bến nước.</t>
         </is>
       </c>
     </row>
@@ -26315,7 +26286,12 @@
           <t>48</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp tiết kiệm và bảo vệ nguồn nước: giáo dục HS biết sử dụng nước tiết kiệm, giữ vệ sinh nguồn nước ở gia đình, trường học và cộng đồng.
+Tích hợp NLS - 1.1.CB2a: HS biết tìm kiếm, chọn lọc hình ảnh/thông tin đơn giản về nét văn hoá dưới sự hướng dẫn của GV và ghi nguồn thông tin phù hợp.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -26347,8 +26323,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Mở đầu bài “Truyền thống yêu nước, cách mạng của đồng bào Bắc Trung Bộ và Nam Trung Bộ”, GV chiếu trò chơi lật mảnh ghép trên màn hình
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động nhóm, GV chiếu bảng chung “Di tích, nhân vật – Nơi có – Điều đáng nhớ”; các nhóm lên điền rồi đọc bảng của nhau
+          <t>Tích hợp QPAN: giáo dục HS tự hào về truyền thống đấu tranh bảo vệ quê hương, biết kính trọng những người có công với đất nước.
 QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
         </is>
       </c>
@@ -26379,7 +26354,8 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS đối chiếu ảnh tư liệu về nhân vật, di tích đã sưu tầm với thông tin trong SGK, chọn ảnh có nguồn tin cậy và ghi rõ nguồn khi kể chuyện trước lớp.</t>
+          <t>Tích hợp lý tưởng cách mạng, đạo đức, lối sống: Giáo dục HS biết trân trọng lòng dũng cảm, tinh thần đoàn kết, ý chí bảo vệ buôn làng, quê hương của các nhân vật lịch sử.
+Tích hợp AI (4.A1.2): HS quan sát GV dùng công cụ AI gợi ý dàn ý/kịch bản kể chuyện đơn giản; nhận biết AI chỉ hỗ trợ, không thay thế tư duy của con người; cùng GV kiểm tra lại thông tin bằng SGK và nguồn chính thống, không sao chép máy móc.</t>
         </is>
       </c>
     </row>
@@ -26413,7 +26389,8 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.
+          <t>Tích hợp lý tưởng cách mạng, đạo đức, lối sống: HS biết giữ gìn di tích, cảnh quan, ứng xử văn minh khi tham quan Cố đô Huế; trân trọng lịch sử và văn hoá dân tộc.
+Tích hợp AI 4.A3.1: HS thảo luận về việc AI có thể hỗ trợ thuyết minh, tìm hiểu di sản nhưng không thay thế hoàn toàn hướng dẫn viên thực sự tại các di sản văn hoá.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -26444,7 +26421,7 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.</t>
+          <t>Tích hợp NLS 3.1.CB2a: HS tạo thẻ giới thiệu ngắn về Cố đô Huế bằng tranh, sơ đồ hoặc slide đơn giản; biết chọn hình ảnh phù hợp, ghi nguồn và kiểm tra lại thông tin bằng SGK trước khi trình bày.</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26455,8 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.</t>
+          <t>Tích hợp lý tưởng cách mạng, đạo đức, lối sống: HS biết trân trọng di sản văn hoá, ứng xử văn minh khi tham quan phố cổ Hội An; không xả rác, không làm hư hại công trình kiến trúc.
+Tích hợp AI 4.A3.1: HS thảo luận về việc có nên dùng AI để thay thế hướng dẫn viên thực sự tại các di sản văn hóa hay không; biết AI có thể hỗ trợ tìm hiểu di sản nhưng thông tin cần được GV kiểm duyệt và đối chiếu với nguồn chính thống.</t>
         </is>
       </c>
     </row>
@@ -26508,7 +26486,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.</t>
+          <t>Tích hợp NLS 1.2.CB2a: HS đối chiếu thông tin/hình ảnh về Hội An từ SGK với nguồn GV cung cấp; biết ghi nguồn, không sử dụng hình ảnh sai chú thích hoặc thông tin chưa kiểm chứng khi giới thiệu di sản.</t>
         </is>
       </c>
     </row>
@@ -26520,14 +26498,14 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 4: Bắc Trung Bộ và Nam Trung Bộ</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì II</t>
+          <t>Bài 21. Lễ hội Cồng chiêng Tây Nguyên</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -26540,7 +26518,12 @@
           <t>55</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp QCN: HS tôn trọng quyền giữ gìn bản sắc văn hoá của đồng bào Tây Nguyên; biết ứng xử văn minh, không chế giễu, không chia sẻ hình ảnh thiếu tôn trọng về lễ hội, trang phục, nhạc cụ của các dân tộc.
+QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -26550,19 +26533,19 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Bắc Trung Bộ và Nam Trung Bộ</t>
+          <t>Chủ đề 5: Nam Bộ</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Bài 21. Lễ hội Cồng chiêng Tây Nguyên</t>
+          <t>Bài 22. Thiên nhiên vùng Nam Bộ (Tiết 1)</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -26572,7 +26555,8 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được nét đặc sắc của lễ hội, nét văn hoá vùng miền nhờ phim tư liệu chính thống.
+          <t>Tích hợp tiết kiệm và bảo vệ nguồn nước: HS nhận biết vùng Nam Bộ có hệ thống sông ngòi, kênh rạch, vùng trũng và biển rộng; từ đó có ý thức không xả rác xuống sông, kênh rạch, biết sử dụng nước tiết kiệm.
+Tích hợp AI 4.D1.1: HS đề xuất ý tưởng dùng cảm biến/AI để theo dõi mực nước, độ mặn, ngập lụt nhằm hỗ trợ người dân Nam Bộ phòng tránh thiên tai và bảo vệ nguồn nước.
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -26592,14 +26576,10 @@
       <c r="D60" s="4" t="inlineStr"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Thiên nhiên vùng Nam Bộ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 22. Thiên nhiên vùng Nam Bộ (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr"/>
       <c r="G60" s="4" t="inlineStr">
         <is>
           <t>57</t>
@@ -26607,8 +26587,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.
-QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+          <t>Tích hợp NLS 1.1.CB2a: HS đọc lược đồ/bản đồ số do GV cung cấp để xác định vị trí sông ngòi, vùng đất, vùng biển đảo của Nam Bộ; biết đọc chú giải, kiểm tra thông tin bằng SGK và không tự truy cập nguồn lạ.</t>
         </is>
       </c>
     </row>
@@ -26627,7 +26606,7 @@
       <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Thiên nhiên vùng Nam Bộ (Tiết 2)</t>
+          <t>Bài 22. Thiên nhiên vùng Nam Bộ (Tiết 3)</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
@@ -26638,7 +26617,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.</t>
+          <t>Tích hợp BVMT: HS nhận biết thuận lợi và khó khăn của môi trường thiên nhiên Nam Bộ; biết nêu việc làm bảo vệ rừng, đất, nguồn nước, kênh rạch, sông biển và giảm tác động của lũ lụt, sạt lở, hạn hán, xâm nhập mặn.</t>
         </is>
       </c>
     </row>
@@ -26657,10 +26636,14 @@
       <c r="D62" s="4" t="inlineStr"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Thiên nhiên vùng Nam Bộ (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr"/>
+          <t>Bài 23. Dân cư và hoạt động sản xuất ở vùng Nam Bộ (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
           <t>59</t>
@@ -26668,7 +26651,9 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS thao tác được các lớp bản đồ số, ảnh vệ tinh để mô tả đặc điểm thiên nhiên của vùng.</t>
+          <t>Tích hợp QCN: HS tôn trọng sự đa dạng dân cư, văn hoá, nghề nghiệp của người dân Nam Bộ; biết đoàn kết, không phân biệt vùng miền, dân tộc, tiếng nói, phong tục.
+Tích hợp AI (4.A1.1): HS nhận diện sự hiện diện của AI trong các khu công nghiệp hiện đại và các trang trại trái cây xuất khẩu ở Nam Bộ.
+QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
     </row>
@@ -26687,14 +26672,10 @@
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Dân cư và hoạt động sản xuất ở vùng Nam Bộ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 23. Dân cư và hoạt động sản xuất ở vùng Nam Bộ (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
           <t>60</t>
@@ -26702,8 +26683,8 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS lập bảng và đọc được biểu đồ dân cư, từ đó giải thích sự phân bố dân cư của vùng.
-QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+          <t>Tích hợp tiết kiệm và bảo vệ nguồn nước: HS hiểu sản xuất nông nghiệp, nuôi trồng thủy sản, công nghiệp ở vùng sông nước cần sử dụng nước tiết kiệm, xử lí nước thải đúng cách, không làm ô nhiễm kênh rạch, sông biển.
+Tích hợp AI (4.A1.1): HS nhận diện sự hiện diện của AI trong các khu công nghiệp hiện đại và các trang trại trái cây xuất khẩu ở Nam Bộ.</t>
         </is>
       </c>
     </row>
@@ -26722,7 +26703,7 @@
       <c r="D64" s="4" t="inlineStr"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Dân cư và hoạt động sản xuất ở vùng Nam Bộ (Tiết 2)</t>
+          <t>Bài 23. Dân cư và hoạt động sản xuất ở vùng Nam Bộ (Tiết 3)</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -26733,7 +26714,8 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS lập bảng và đọc được biểu đồ dân cư, từ đó giải thích sự phân bố dân cư của vùng.</t>
+          <t>Tích hợp NLS 3.1.CB2a: HS dùng bảng/sơ đồ số đơn giản để phân loại hoạt động sản xuất; GV kiểm duyệt thông tin trước khi HS sử dụng; HS biết đối chiếu thông tin với SGK, hình 1, hình 4 và nguồn do GV cung cấp.
+Tích hợp BVMT và ATGT: HS biết sản xuất, giao thông đường thủy cần gắn với bảo vệ môi trường, không xả rác xuống sông, kênh rạch; biết đội áo phao, ngồi ngay ngắn, đi theo hướng dẫn của người lớn và lực lượng chức năng khi tham gia phương tiện đường thủy.</t>
         </is>
       </c>
     </row>
@@ -26752,10 +26734,14 @@
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Bài 23. Dân cư và hoạt động sản xuất ở vùng Nam Bộ (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr"/>
+          <t>Bài 24. Một số nét văn hoá và truyền thống yêu nước, cách mạng của đồng bào Nam Bộ (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
           <t>62</t>
@@ -26763,7 +26749,8 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mở lược đồ số của vùng trên máy chiếu, phóng to để tìm nơi phân bố các hoạt động sản xuất và điền vào sơ đồ tư duy của nhóm.</t>
+          <t>Tích hợp ATGT đường thuỷ và BVMT: HS nhận biết đời sống sông nước gắn với an toàn, trật tự, giao thông đường thuỷ; biết chấp hành quy định khi đi ghe, xuồng, phà, bến tàu; có ý thức giữ gìn kênh rạch, không xả rác xuống sông để góp phần bảo vệ môi trường và cuộc sống bình yên của cộng đồng.
+QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
         </is>
       </c>
     </row>
@@ -26782,14 +26769,10 @@
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Một số nét văn hoá và truyền thống yêu nước, cách mạng của đồng bào Nam Bộ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 24. Một số nét văn hoá và truyền thống yêu nước, cách mạng của đồng bào Nam Bộ (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr"/>
       <c r="G66" s="4" t="inlineStr">
         <is>
           <t>63</t>
@@ -26797,8 +26780,8 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được nét đặc sắc của lễ hội, nét văn hoá vùng miền nhờ phim tư liệu chính thống.
-QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
+          <t>Tích hợp lý tưởng cách mạng, đạo đức, lối sống: HS biết trân trọng tinh thần yêu nước, lòng dũng cảm, sự kiên trung của các nhân vật lịch sử; biết biến lòng biết ơn thành hành động cụ thể như chăm học, sống trung thực, đoàn kết, giữ gìn truyền thống tốt đẹp của quê hương.
+Tích hợp AI (4.A1.2): HS quan sát GV dùng công cụ AI gợi ý dàn ý cho đoạn văn bày tỏ cảm nghĩ; nhận biết AI chỉ hỗ trợ, không thay thế suy nghĩ, cảm xúc của người viết; cùng GV kiểm tra lại thông tin bằng SGK; HS tự viết bằng lời của mình.</t>
         </is>
       </c>
     </row>
@@ -26817,10 +26800,14 @@
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Một số nét văn hoá và truyền thống yêu nước, cách mạng của đồng bào Nam Bộ (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
+          <t>Bài 25. Thành phố Hồ Chí Minh (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>64</t>
@@ -26828,7 +26815,9 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được nét đặc sắc của lễ hội, nét văn hoá vùng miền nhờ phim tư liệu chính thống.</t>
+          <t>Tích hợp lý tưởng cách mạng: HS tự hào về Thành phố Hồ Chí Minh, thành phố mang tên Bác; biết giữ gìn hình ảnh đô thị văn minh, nghĩa tình.
+Tích hợp AI 4.A2.1: HS nhận diện Thành phố Hồ Chí Minh là thành phố thông minh, nơi AI hỗ trợ điều hành giao thông và dịch vụ công.
+QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
     </row>
@@ -26847,14 +26836,10 @@
       <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Thành phố Hồ Chí Minh (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 25. Thành phố Hồ Chí Minh (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="inlineStr">
         <is>
           <t>65</t>
@@ -26862,8 +26847,7 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.
-QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+          <t>Tích hợp NLS 3.1.CB2a: Học sinh sử dụng thông tin, hình ảnh từ SGK và nguồn học liệu do giáo viên cung cấp để lập thẻ/sơ đồ/slide giới thiệu địa danh; biết ghi nguồn, kiểm tra thông tin và không chia sẻ hình ảnh sai chú thích.</t>
         </is>
       </c>
     </row>
@@ -26882,10 +26866,14 @@
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Thành phố Hồ Chí Minh (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
+          <t>Bài 26. Địa đạo Củ Chi</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>66</t>
@@ -26893,7 +26881,8 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.</t>
+          <t>Tích hợp QPAN: HS biết ơn chiến sĩ cách mạng, hiểu giá trị lịch sử của Địa đạo Củ Chi; có ý thức giữ gìn di tích.
+QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
     </row>
@@ -26912,12 +26901,12 @@
       <c r="D70" s="4" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Địa đạo Củ Chi</t>
+          <t>Bài 27. Ôn tập (Tiết 1)</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -26927,8 +26916,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS phân biệt được hiện vật, tư liệu gốc với hình phục dựng do máy tạo.
-QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
+          <t>Tích hợp NLS 1.1.CB2a: HS quan sát bản đồ số Việt Nam do GV trình chiếu để đối chiếu vị trí hai vùng khi phân loại thông tin và hoàn thành bảng so sánh.</t>
         </is>
       </c>
     </row>
@@ -26947,14 +26935,10 @@
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bài 27. Ôn tập (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 27. Ôn tập (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="inlineStr">
         <is>
           <t>68</t>
@@ -26962,7 +26946,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mở bản đồ số Việt Nam trên máy chiếu, phóng to để chỉ vị trí và kể tên các tỉnh, thành phố của vùng Bắc Trung Bộ và Nam Trung Bộ rồi điền vào phiếu ôn tập.</t>
+          <t>Tích hợp lý tưởng cách mạng, đạo đức, lối sống: khi đóng vai hướng dẫn viên, HS giới thiệu đúng, thể hiện niềm tự hào về di sản, truyền thống lịch sử của các vùng; có ý thức giữ gìn di tích, ứng xử văn minh.</t>
         </is>
       </c>
     </row>
@@ -26974,27 +26958,27 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Nam Bộ</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
       <c r="D72" s="4" t="inlineStr"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Bài 27. Ôn tập (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr"/>
+          <t>Kiểm tra định kì cuối năm học</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.2 CB2a: HS chọn tranh ảnh về vùng Nam Bộ có nguồn tin cậy trong số tư liệu đã sưu tầm để làm bài giới thiệu và ghi rõ nguồn dưới mỗi ảnh.</t>
-        </is>
-      </c>
+      <c r="H72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -27011,7 +26995,7 @@
       <c r="D73" s="4" t="inlineStr"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì cuối năm học</t>
+          <t>Nhận xét, chữa bài kiểm tra định kì cuối năm học</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -27454,7 +27438,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Digital competence 2.1 CB2a: Pupils look at digital flashcards on the screen, then ask and answer in pairs about their friends’ countries and nationalities.
+          <t>Digital Competency (3.1CB2a): Create simple digital content: Pupils learn to create simple digital pupil cards (including text and images like flags) using basic tools (e.g., Paint, tablet drawing apps) for learning and presentation purposes.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -27525,48 +27509,47 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
+          <t>Digital Competence 2.2CB2a: Recognize where data is organized/stored (e.g., recognizing that time and daily routine information is structured and displayed on clocks, timetables, or digital schedules).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2 — Time and daily routines</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Unit 2 — Time and daily routines — Lesson 2 (Daily routines) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
           <t>Digital competence Domain 1 (Basic, level 2): In Unit 2 Time and daily routines, the teacher shows a set of pictures of daily activities with clock faces and plays the model audio
 Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise to listen and choose the right picture and drag the clock hands to the time heard; the computer marks it instantly, so pupils notice when they still confuse times with past and times with to
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Unit 2 — Time and daily routines</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Unit 2 — Time and daily routines — Lesson 2 (Daily routines) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In Unit 2 Time and daily routines, the teacher shows a set of pictures of daily activities with clock faces and plays the model audio
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise to listen and choose the right picture and drag the clock hands to the time heard; the computer marks it instantly, so pupils notice when they still confuse times with past and times with to
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
@@ -27667,8 +27650,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 2 Time and daily routines, the teacher shows a digital clock face with pictures of daily activities and plays the model audio files of asking and telling the time
-Digital competence Domain 2 (Basic, level 2): The teacher shows the class's blank daily timetable on the screen; each pair of pupils asks and answers about the time they get up, go to school and have dinner, then reads it out for the teacher to fill in the table
+          <t>Digital Competence 3.1CB2b: Choose ways to express oneself through creating a personalized timetable. Pupils select specific daily activities and visual styles to reflect their own identity and routine.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -27739,118 +27721,117 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
+          <t>Digital Competency (3.2CB2a): Select ways to modify and refine information (weekly schedule): Pupils learn how to identify, select, and update correct information in a digital weekly schedule context when presented with incomplete or incorrect data.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3 — My week</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3 — My week — Lesson 2 (Activities in the week) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence Domain 2 (Basic, level 2): In Unit 3 My week, speaking part, the teacher shows the class's blank timetable on the screen; each pair asks and answers in English about which subjects they have on which day
+Digital competence Domain 3 (Basic, level 2): Each group makes a page introducing their school week: choose subject icons, write the days next to them and write two sentences in English
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3 — My week</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3 — My week — Lesson 2 (Activities in the week) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3 — My week</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Unit 3 — My week — Lesson 3 (Skills: Listen–Read) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
           <t>Digital competence Domain 1 (Basic, level 2): In the pronunciation part of Unit 3 My week, the teacher plays the audio file of words and sentences with the sound u, first slowly and then at normal speed; pupils listen
 Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the words with the new sound, and match sentences with pictures; the computer marks it instantly, so pupils notice which words they still confuse
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Unit 3 — My week</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Unit 3 — My week — Lesson 2 (Activities in the week) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 2 (Basic, level 2): In Unit 3 My week, speaking part, the teacher shows the class's blank timetable on the screen; each pair asks and answers in English about which subjects they have on which day
-Digital competence Domain 3 (Basic, level 2): Each group makes a page introducing their school week: choose subject icons, write the days next to them and write two sentences in English
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Unit 3 — My week</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Unit 3 — My week — Lesson 2 (Activities in the week) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Unit 3 — My week</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Unit 3 — My week — Lesson 3 (Skills: Listen–Read) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the pronunciation part of Unit 3 My week, the teacher plays the audio file of words and sentences with the sound u, first slowly and then at normal speed; pupils listen
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the words with the new sound, and match sentences with pictures; the computer marks it instantly, so pupils notice which words they still confuse
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -27881,8 +27862,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 3 My week, the teacher shows a set of cards for the days of the week with audio files; pupils listen, then put the days in the right order on the screen
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing days in sentences; the computer marks it instantly, so pupils notice when they still confuse two days that sound alike
+          <t>Digital Competency (2.4CB2a): Select simple digital tools for group collaboration: Pupils work in groups to choose a digital template/table to organize and present their group’s weekly or weekend activities.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -28023,8 +28003,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In Unit 4 My birthday party, the teacher shows a set of pictures of things and activities at a party with an audio recording; pupils listen and match the words with the pictures
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the right picture, and fill in the missing words in invitations; the computer marks it instantly, so pupils notice when they still confuse two similar words
+          <t>Digital Competency (1.2CB2a): Detect the accuracy of dates in a listening task: Pupils can identify whether the date mentioned in a digital audio clip/invitation matches the visual information provided on the screen, fostering critical thinking in digital environments.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -28130,7 +28109,7 @@
       <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Digital competence Domain 1 (Basic, level 2): To start Unit 5 Things we can do, the teacher shows a set of activity pictures with model audio; pupils listen and match the activities with the pictures
-Digital competence Domain 2 (Basic, level 2): The teacher shows a three-column table of friends' names, what they can do and what they want to learn; each pair asks and answers in English and then reads out the answers for the teacher to fill in
+Digital competence Domain 2 (Basic, level 2): Pairs ask and answer, T fills a table (name / can do / wants to learn); Ss introduce friends from it
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -28165,118 +28144,117 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
+          <t>Digital Competency (2.6CB2a): Identify digital identity (abilities/hobbies): Pupils recognize that sharing and selecting their abilities (e.g., picking an avatar or a skill badge on hoclieu.vn) is a way to represent themselves (their identity) in a digital environment.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5 — Things we can do</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5 — Things we can do — Lesson 2 (He/She can) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence Domain 5 (Basic, level 2): In the practice part of Unit 5 Things we can do, the teacher opens an interactive exercise: listen and choose the picture and fill in the missing words in sentences about abilities
+Digital competence Domain 2 (Basic, level 2): The teacher records the exchanges of a few pairs and plays them to the class; pupils comment using the criteria: full sentences, clear pronunciation, correct patterns
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5 — Things we can do</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5 — Things we can do — Lesson 2 (He/She can) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5 — Things we can do</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Unit 5 — Things we can do — Lesson 3 (Skills: Listen–Read) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
           <t>Digital competence Domain 1 (Basic, level 2): In the skills part of Unit 5 Things we can do, the teacher opens the song and learning materials of the lesson in the education sector's digital learning resource library and shows pupils the way…
 Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing words in sentences; the computer marks it instantly, so pupils notice where they went wrong and listen to that part again
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5 — Things we can do</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5 — Things we can do — Lesson 2 (He/She can) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 5 (Basic, level 2): In the practice part of Unit 5 Things we can do, the teacher opens an interactive exercise: listen and choose the picture and fill in the missing words in sentences about abilities
-Digital competence Domain 2 (Basic, level 2): The teacher records the exchanges of a few pairs and plays them to the class; pupils comment using the criteria: full sentences, clear pronunciation, correct patterns
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5 — Things we can do</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5 — Things we can do — Lesson 2 (He/She can) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5 — Things we can do</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr"/>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Unit 5 — Things we can do — Lesson 3 (Skills: Listen–Read) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the skills part of Unit 5 Things we can do, the teacher opens the song and learning materials of the lesson in the education sector's digital learning resource library and shows pupils the way…
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing words in sentences; the computer marks it instantly, so pupils notice where they went wrong and listen to that part again
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
@@ -28307,8 +28285,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 5 Things we can do, the teacher shows a set of activity pictures with model audio; pupils listen and match the activities with the pictures
-Digital competence Domain 2 (Basic, level 2): The teacher shows a three-column table of friends' names, what they can do and what they want to learn; each pair asks and answers in English and then reads out the answers for the teacher to fill in
+          <t>Digital Competency (2.2CB2a): Identify basic citation methods (Imitating digital models): Pupils recognize digital audio/video from Hoclieu.vn as the standard "source" and demonstrate the ability to "cite" it by imitating the exact pronunciation, rhythm, and melody.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -28694,118 +28671,117 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
+          <t>Digital Competence: CB2a Interaction through various digital technologies. (Students observe and interact with review content on the projection screen)
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7 — Our timetables</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
+      <c r="D49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7 — Our timetables — Lesson 2 (Subjects on days) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence Domain 1 (Basic, level 2): In Unit 7 Our timetables, the teacher shows a sample timetable with audio files; pupils listen, then point to the right subject on the right day
+Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing subjects in the timetable; the computer marks it instantly, so pupils notice which subjects they misheard
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7 — Our timetables</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7 — Our timetables — Lesson 2 (Subjects on days) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7 — Our timetables</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Unit 7 — Our timetables — Lesson 3 (Skills: Listen–Read) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
           <t>Digital competence Domain 2 (Basic, level 2): In the practice part of Unit 7, the teacher plays the lesson's song on the screen for the whole class to sing along, then records the questions and answers about the timetable of a few…
 Digital competence Domain 3 (Basic, level 2): Each group makes a picture timetable: choose subject icons, write the days and two sentences in English introducing their favourite day
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7 — Our timetables</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr"/>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7 — Our timetables — Lesson 2 (Subjects on days) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In Unit 7 Our timetables, the teacher shows a sample timetable with audio files; pupils listen, then point to the right subject on the right day
-Digital competence Domain 5 (Basic, level 2): The teacher opens an interactive exercise: listen and choose the picture, and fill in the missing subjects in the timetable; the computer marks it instantly, so pupils notice which subjects they misheard
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7 — Our timetables</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7 — Our timetables — Lesson 2 (Subjects on days) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7 — Our timetables</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Unit 7 — Our timetables — Lesson 3 (Skills: Listen–Read) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 2 (Basic, level 2): In the practice part of Unit 7, the teacher plays the lesson's song on the screen for the whole class to sing along, then records the questions and answers about the timetable of a few…
-Digital competence Domain 3 (Basic, level 2): Each group makes a picture timetable: choose subject icons, write the days and two sentences in English introducing their favourite day
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
@@ -28836,8 +28812,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 2 (Basic, level 2): In the practice part of Unit 7, the teacher plays the lesson's song on the screen for the whole class to sing along, then records the questions and answers about the timetable of a few…
-Digital competence Domain 3 (Basic, level 2): Each group makes a picture timetable: choose subject icons, write the days and two sentences in English introducing their favourite day
+          <t>Digital Competence: CB2a Select simple digital technologies to interact. (Students interact with chants through video/audio on projector/speaker)
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -29048,8 +29023,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): To start Unit 8 My favourite subjects, the teacher shows a set of pictures of school subjects with model audio files; pupils listen, then match the subject names with the pictures
-Digital competence Domain 2 (Basic, level 2): The teacher shows the class survey table of favourite subjects; each pair asks and answers in English and then reads out the answers for the teacher to tick
+          <t>Digital Competence: CB2a Select simple digital technologies for interaction. (Students interact with the warm-up chant/video on the screen)
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -29260,8 +29234,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 9 “Our sports day”, the teacher shows the pictures on the screen and plays the audio, pausing after each part so pupils tick
-Digital competence Domain 2 (Basic, level 2): In the Let's chant activity, the teacher plays the chant with words moving in rhythm on the screen so the whole class chants together in the right rhythm
+          <t>Digital Competence (3.1CB2a): Create simple digital content (e.g., design a Sports Day poster using simple software like MS Paint or PowerPoint).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -29332,118 +29305,117 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
+          <t>Digital Competence (2.2CB2a): Share personal information (e.g., sharing where they went during the holidays) with others through simple digital technologies (simulating sending a message or sharing a photo).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10 — Our summer holidays</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+      <c r="D67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10 — Our summer holidays — Lesson 2 (Holiday activities) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and number activity of Unit 10 “Our summer holidays”, the teacher shows the pictures on the screen and plays the audio, pausing after each part so pupils can number them
+Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song Were you on the beach yesterday? with scrolling lyrics on the screen for the whole class to sing together
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10 — Our summer holidays</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
+      <c r="D68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10 — Our summer holidays — Lesson 2 (Holiday activities) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10 — Our summer holidays</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Unit 10 — Our summer holidays — Lesson 3 (Skills: Listen–Read) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
           <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 10 “Our summer holidays”, the teacher plays the model audio of the sound ere in the word were
 Digital competence Domain 5 (Basic, level 2): In the Warm-up game Board race, the teacher shows the topic on the screen, and two teams take turns writing words they have learnt
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10 — Our summer holidays</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr"/>
-      <c r="D67" s="4" t="inlineStr"/>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10 — Our summer holidays — Lesson 2 (Holiday activities) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and number activity of Unit 10 “Our summer holidays”, the teacher shows the pictures on the screen and plays the audio, pausing after each part so pupils can number them
-Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song Were you on the beach yesterday? with scrolling lyrics on the screen for the whole class to sing together
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10 — Our summer holidays</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr"/>
-      <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10 — Our summer holidays — Lesson 2 (Holiday activities) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10 — Our summer holidays</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr"/>
-      <c r="D69" s="4" t="inlineStr"/>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Unit 10 — Our summer holidays — Lesson 3 (Skills: Listen–Read) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 10 “Our summer holidays”, the teacher plays the model audio of the sound ere in the word were
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Board race, the teacher shows the topic on the screen, and two teams take turns writing words they have learnt
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
@@ -29474,8 +29446,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 10 “Our summer holidays”, the teacher shows pictures of summer holidays on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the Point and say activity, the teacher shows a shared table “Places visited – Things done”; pairs ask and answer, then come up to write their partner's answers in the table
+          <t>Digital Competence (Integrated): CB2a: Select simple digital tools and technologies for collaborative processes (specifically: choosing a tool to collaborate on telling summer holiday stories).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -29710,120 +29681,118 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
+          <t>Digital Competence (2.1CB2a): Select simple digital technologies to interact: Choose appropriate simple digital forms (e.g., text message or voice message) to describe their home address to friends.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11 — My home</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr"/>
+      <c r="D78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11 — My home — Lesson 1 (Rooms &amp; places at home) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 11 “My home”, the teacher shows pictures of things in the house with the words and plays the model audio
+Digital competence Domain 2 (Basic, level 2): In the Warm-up game Whispering, after each round of passing the message the teacher shows the original sentence on the screen; the two teams compare what they said with the original
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11 — My home</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
+      <c r="D79" s="4" t="inlineStr"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11 — My home — Lesson 2 (Location of things) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Digital Competence (1.2CB2a): Detect the accuracy of the location information heard (from the digital audio recording) by comparing it with visual data (pictures).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11 — My home</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Unit 11 — My home — Lesson 2 (Location of things) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
           <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 11 “My home”, the teacher plays the model audio of the letter sounds in the lesson
 Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song My house with scrolling lyrics on the screen for the whole class to sing; then divides the class into two groups to sing in turn following the highlighted lyrics and listen…
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11 — My home</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr"/>
-      <c r="D78" s="4" t="inlineStr"/>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11 — My home — Lesson 1 (Rooms &amp; places at home) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 11 “My home”, the teacher shows pictures of things in the house with the words and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the Warm-up game Whispering, after each round of passing the message the teacher shows the original sentence on the screen; the two teams compare what they said with the original
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11 — My home</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr"/>
-      <c r="D79" s="4" t="inlineStr"/>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11 — My home — Lesson 2 (Location of things) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 11 “My home”, the teacher shows pictures of things in the house with the words and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the Warm-up game Whispering, after each round of passing the message the teacher shows the original sentence on the screen; the two teams compare what they said with the original
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11 — My home</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr"/>
-      <c r="D80" s="4" t="inlineStr"/>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Unit 11 — My home — Lesson 2 (Location of things) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 11 “My home”, the teacher plays the model audio of the letter sounds in the lesson
-Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song My house with scrolling lyrics on the screen for the whole class to sing; then divides the class into two groups to sing in turn following the highlighted lyrics and listen…
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
@@ -29854,8 +29823,7 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 11 “My home”, the teacher plays the model audio of the letter sounds in the lesson
-Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song My house with scrolling lyrics on the screen for the whole class to sing; then divides the class into two groups to sing in turn following the highlighted lyrics and listen…
+          <t>Digital Competence (3.1CB2a): Create simple digital content (Draw/Describe the house using simple drawing software like Paint or typing text).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -29926,8 +29894,7 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 12 “Jobs”, the teacher shows pictures of people at work with the job names on the screen and plays the model audio
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Guess the job, the teacher shows photos of objects linked to jobs one by one, such as a stethoscope, a builder's ruler, a chalkboard
+          <t>Digital Competence (2.2CB2a): Recognize where to organize data: Identify the correct folder, file, or digital section to store and share information about "Dream Jobs" on the computer.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -29998,48 +29965,47 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
+          <t>Digital Competence (NLS): - 1.2CB2a: Evaluate the accuracy of career information (Specifically: Check if the information regarding jobs and workplaces matches the provided visual or audio data).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12 — Jobs</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr"/>
+      <c r="D86" s="4" t="inlineStr"/>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Unit 12 — Jobs — Lesson 2 (Workplaces &amp; wishes) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
           <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 12 “Jobs”, the teacher plays the model audio of the job words, first slowly and then at normal speed, and shows the words with marks…
 Digital competence Domain 5 (Basic, level 2): In the Warm-up game Lip-reading, the teacher shows a job word to one pupil only, who mouths it silently for the group to guess
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>Unit 12 — Jobs</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr"/>
-      <c r="D86" s="4" t="inlineStr"/>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>Unit 12 — Jobs — Lesson 2 (Workplaces &amp; wishes) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 12 “Jobs”, the teacher plays the model audio of the job words, first slowly and then at normal speed, and shows the words with marks…
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Lip-reading, the teacher shows a job word to one pupil only, who mouths it silently for the group to guess
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
@@ -30070,8 +30036,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 12 “Jobs”, the teacher shows pictures of people at work with the job names on the screen and plays the model audio
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Guess the job, the teacher shows photos of objects linked to jobs one by one, such as a stethoscope, a builder's ruler, a chalkboard
+          <t>Digital Competence (NLS): - 3.1CB2b: Choose ways to express oneself through creating content (Express oneself through a writing piece about family members).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -30142,8 +30107,7 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 13 “Appearance”, the teacher shows pictures of characters with different appearances and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Character – Appearance”; pairs ask and answer about the characters in the picture and then come up to fill in their sentences
+          <t>Digital Competence (NLS): 4.2CB2a: Choose simple ways to protect personal data (photos). (e.g., Understanding that photos of one's appearance are personal data and shouldn't be shared with strangers).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -30214,8 +30178,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 13 “Appearance”, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the person described
-Digital competence Domain 2 (Basic, level 2): In the Warm-up, the teacher plays the song What do your parents look like? with scrolling lyrics on the screen for the whole class to sing
+          <t>Digital Competence (NLS):3.2CB2a: Choose ways to modify and refine descriptive sentences (Students can select appropriate adjectives or phrases to correct or improve a digital description of someone's appearance).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -30286,8 +30249,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 13 “Appearance”, the teacher plays the model audio of sentences describing appearance
-Digital competence Domain 5 (Basic, level 2): In the Warm-up message-passing game, after each turn the teacher shows the original sentence describing a person on the screen; the two teams compare what they said with the original sentence
+          <t>Digital Competence (NLS):2.4CB2a: Select simple digital tools for group collaboration (e.g., choose between creating a digital slide or a paper poster to present survey results).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -30358,8 +30320,7 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Time – What I do”; pairs ask and answer about each other's daily timetables, then come up to write their sentences
+          <t>Digital Competence (1.3CB2b):Recognize where data is organized (sequence of activities).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -30430,8 +30391,7 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the Warm-up game Change chairs, the teacher shows the commands on the screen for the whole class to read together; pupils listen and change seats if the sentence is true for them
+          <t>Digital Competence: - 1.2CB2a: Detect the reliability of time information. (Specifically: Identify illogical or incorrect time information presented in digital formats like slides or online schedules).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -30502,8 +30462,7 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Vocabulary activity of Unit 14 “Daily activities”, the teacher shows pictures of daily activities with the new words on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Time – What I do”; pairs ask and answer about each other's daily timetables, then come up to write their sentences
+          <t>Competences:  Digital Competence 3.1CB2a: Identify how to create content (Activity Diary).
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -30574,9 +30533,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 15 “My family's weekends”, the teacher shows pictures of places in the town with their names on the screen and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows a shared table “Weekend places – What people do there”; pairs ask and answer and then come up to fill in their sentences
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -30716,9 +30673,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and repeat of Unit 15 “My family's weekends”, the teacher plays the model audio, first slowly and then at normal speed, and shows the sentences with stress marks…
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Matching, the teacher shows two shuffled columns of words and pictures; groups try matching them and then click check
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31028,8 +30983,7 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 16 “Weather”, the teacher plays the model audio of the two sounds learnt, first slowly and then at normal speed, and shows example sentences with…
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Slap the board, the teacher shows the words learnt on the screen; two teams listen to the teacher and come up to touch the right word
+          <t>Digital Competence 3.2CB2a (Refining and integrating content): Pupils can collect, refine (edit/adjust), and integrate weather data from different sources (text, pictures, personal experience) to create a structured weather report/chart.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -31100,120 +31054,118 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
+          <t>Digital Competency (2.5CB2a - Choosing simple behavioral standards - Urban Civility): Pupils can identify and choose correct behaviors (civility) when interacting with digital simulations of traffic situations (choosing the "civil" action on a digital platform/game).
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Unit 17 — In the city</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr"/>
+      <c r="D117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Unit 17 — In the city — Lesson 1 (Places in a city) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 17 “In the city”, the teacher shows a street map on the screen and plays the model audio of sentences giving directions
+Digital competence Domain 5 (Basic, level 2): In the speaking activity, the teacher shows a neighbourhood map marked with a starting point and a destination; pairs take turns giving directions in English
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Unit 17 — In the city</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr"/>
+      <c r="D118" s="4" t="inlineStr"/>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Unit 17 — In the city — Lesson 2 (Giving directions) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Digital Competency 1.2CB2a (Detecting the reliability of directions): Pupils can evaluate whether the direction heard matches the visual map/cues provided in the book to ensure the information is reliable before choosing the answer.
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Unit 17 — In the city</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr"/>
+      <c r="D119" s="4" t="inlineStr"/>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Unit 17 — In the city — Lesson 2 (Giving directions) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
           <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 17 “In the city”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick the places mentioned
 Digital competence Domain 5 (Basic, level 2): In the Warm-up game Memory game, the teacher shows a set of cards with direction and place words and then hides them one by one; groups remember and name the missing card
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Unit 17 — In the city</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr"/>
-      <c r="D117" s="4" t="inlineStr"/>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>Unit 17 — In the city — Lesson 1 (Places in a city) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 17 “In the city”, the teacher shows a street map on the screen and plays the model audio of sentences giving directions
-Digital competence Domain 5 (Basic, level 2): In the speaking activity, the teacher shows a neighbourhood map marked with a starting point and a destination; pairs take turns giving directions in English
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Unit 17 — In the city</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr"/>
-      <c r="D118" s="4" t="inlineStr"/>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>Unit 17 — In the city — Lesson 2 (Giving directions) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 17 “In the city”, the teacher shows a street map on the screen and plays the model audio of sentences giving directions
-Digital competence Domain 5 (Basic, level 2): In the speaking activity, the teacher shows a neighbourhood map marked with a starting point and a destination; pairs take turns giving directions in English
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Unit 17 — In the city</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr"/>
-      <c r="D119" s="4" t="inlineStr"/>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>Unit 17 — In the city — Lesson 2 (Giving directions) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 17 “In the city”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick the places mentioned
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Memory game, the teacher shows a set of cards with direction and place words and then hides them one by one; groups remember and name the missing card
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
@@ -31244,9 +31196,7 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Listen and tick of Unit 17 “In the city”, the teacher shows the pictures on the screen and plays the audio, pausing after each part for pupils to tick the places mentioned
-Digital competence Domain 5 (Basic, level 2): In the Warm-up game Memory game, the teacher shows a set of cards with direction and place words and then hides them one by one; groups remember and name the missing card
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
@@ -31316,8 +31266,7 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Look, listen and repeat of Unit 18 “At the shopping centre”, the teacher shows a picture of a shopping centre with the names of the shops and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Shop – Things you can buy there”; pairs ask and answer and then come up to fill in their sentences
+          <t>Digital Competency 4.1CB2b (Distinguishing simple risks - shopping safety): Identify potential risks at a shopping centre (e.g., getting lost, keeping personal belongings safe) and understand that knowing the exact location of shops helps minimize these risks.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -31458,8 +31407,7 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the activity Look, listen and repeat of Unit 18 “At the shopping centre”, the teacher shows a picture of a shopping centre with the names of the shops and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Shop – Things you can buy there”; pairs ask and answer and then come up to fill in their sentences
+          <t>Digital Competency (3.1CB2a): Create simple digital content (a discount poster). Students learn how to organize information (items, prices, discounts) into a visual digital format.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -31530,120 +31478,116 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Unit 19 — The animal world</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr"/>
+      <c r="D129" s="4" t="inlineStr"/>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Unit 19 — The animal world — Lesson 1 (Wild animals) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 19 “The animal world”, the teacher shows pictures of animals on the screen and plays the model audio of the describing sentences
+Digital competence Domain 5 (Basic, level 2): In the Warm-up animal-guessing game, the teacher shows mostly covered pictures; groups guess the names in English and raise their hands to answer
+Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Unit 19 — The animal world</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr"/>
+      <c r="D130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>Unit 19 — The animal world — Lesson 2 (Describing animals) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Unit 19 — The animal world</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr"/>
+      <c r="D131" s="4" t="inlineStr"/>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Unit 19 — The animal world — Lesson 2 (Describing animals) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
           <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 19, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the animal mentioned
 Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Animal – Habitat – Food”; pairs ask and answer and then come up to fill in their sentences
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>Unit 19 — The animal world</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr"/>
-      <c r="D129" s="4" t="inlineStr"/>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>Unit 19 — The animal world — Lesson 1 (Wild animals) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G129" s="4" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 19 “The animal world”, the teacher shows pictures of animals on the screen and plays the model audio of the describing sentences
-Digital competence Domain 5 (Basic, level 2): In the Warm-up animal-guessing game, the teacher shows mostly covered pictures; groups guess the names in English and raise their hands to answer
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>Unit 19 — The animal world</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr"/>
-      <c r="D130" s="4" t="inlineStr"/>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>Unit 19 — The animal world — Lesson 2 (Describing animals) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G130" s="4" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and repeat activity of Unit 19 “The animal world”, the teacher shows pictures of animals on the screen and plays the model audio of the describing sentences
-Digital competence Domain 5 (Basic, level 2): In the Warm-up animal-guessing game, the teacher shows mostly covered pictures; groups guess the names in English and raise their hands to answer
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Unit 19 — The animal world</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr"/>
-      <c r="D131" s="4" t="inlineStr"/>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>Unit 19 — The animal world — Lesson 2 (Describing animals) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G131" s="4" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 19, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the animal mentioned
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Animal – Habitat – Food”; pairs ask and answer and then come up to fill in their sentences
-Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
-        </is>
-      </c>
-    </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
@@ -31674,8 +31618,7 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Listen and tick activity of Unit 19, the teacher shows pictures on the screen and plays the audio, pausing after each part so pupils tick the animal mentioned
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Animal – Habitat – Food”; pairs ask and answer and then come up to fill in their sentences
+          <t>Competency 3.1CB2b: Express oneself (drawing/telling about favorite animals). Students use their creativity to draw and their speaking skills to present their personal connection to the animal world.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -31746,8 +31689,7 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 20 “At summer camp”, the teacher shows pictures of summer camp activities with their names and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Summer camp activity – Why I like it”; pairs ask and answer and then come up to fill in their sentences
+          <t>Digital Competency (2.6CB2b): Protecting online reputation (when sharing photos). Students recognize which photos are appropriate to share on social media to maintain a positive digital image for themselves and their friends.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -31888,8 +31830,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>Digital competence Domain 1 (Basic, level 2): In the Look, listen and repeat activity of Unit 20 “At summer camp”, the teacher shows pictures of summer camp activities with their names and plays the model audio
-Digital competence Domain 2 (Basic, level 2): In the speaking activity, the teacher shows the shared table “Summer camp activity – Why I like it”; pairs ask and answer and then come up to fill in their sentences
+          <t>Digital Competency 2.4CB2a (Choose digital collaboration tools for group planning): Students can discuss and select appropriate digital platforms (e.g., Padlet, Zalo, PowerPoint) to collect images and plan their group's project presentation.
 Life skills: Communication skills: confidently greet others and introduce themselves in simple sentences.</t>
         </is>
       </c>
@@ -33532,6 +33473,7 @@
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Vật liệu và dụng cụ trồng hoa, cây cảnh trong chậu”, GV chiếu ảnh phóng to từng loại giá thể, phân bón, chậu và dụng cụ như xẻng nhỏ, bình tưới
 Năng lực số Miền 5 (Cơ bản, bậc 2): GV chiếu vài tình huống trồng cây trong chậu và cho HS chọn bộ vật liệu, dụng cụ phù hợp cho từng loại cây; máy báo đúng
+STEM: Chậu hoa, cây cảnh mini (Công nghệ – Mĩ thuật) — dạy thay cho tiết này.
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
@@ -33715,6 +33657,7 @@
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Chậu hoa và cây cảnh mini”, GV chiếu ảnh phóng to nhiều kiểu chậu mini cùng loại cây phù hợp với từng chậu; HS gọi tên cây
 Năng lực số Miền 5 (Cơ bản, bậc 2): GV chiếu vài tình huống chọn chậu và cây cho góc học tập, ban công, lớp học; HS chọn phương án phù hợp rồi giải thích theo điều kiện ánh sáng, không gian
+STEM: Chậu hoa, cây cảnh mini (Công nghệ – Mĩ thuật) — dạy thay cho tiết này.
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
@@ -34620,7 +34563,7 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 1: Âm thanh ngày mới — Vận dụng – Sáng tạo (Tổng kết chủ đề 1)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -34755,7 +34698,7 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 2: Giai điệu quê hương — Vận dụng – Sáng tạo (Tổng kết chủ đề 2)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -34772,7 +34715,7 @@
         <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở tiết tổng kết chủ đề “Giai điệu quê hương”, GV mở bản thu các bài đã học và một vài trích đoạn dân ca cùng vùng miền; HS nghe đoán tên bài
 Năng lực số Miền 3 (Cơ bản, bậc 2): Các nhóm dàn dựng tiết mục hát kết hợp gõ đệm, vận động; GV quay lại rồi chiếu cho cả lớp xem
-KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+QPAN: Chọn bài hát ca ngợi quê hương, đất nước, hoà bình; liên hệ bản đồ hành chính Việt Nam và chủ quyền của Việt Nam đối với quần đảo Hoàng Sa, Trường Sa.</t>
         </is>
       </c>
     </row>
@@ -34893,7 +34836,7 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 3: Thầy cô với chúng em — Vận dụng – Sáng tạo (Tổng kết chủ đề 3)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -35027,7 +34970,7 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 4: Vui đón Tết — Vận dụng – Sáng tạo (Tổng kết chủ đề 4)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -35229,7 +35172,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 5: Thiên nhiên tươi đẹp — Vận dụng – Sáng tạo (Tổng kết chủ đề 5)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -35368,7 +35311,7 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 6: Tình bạn tuổi thơ — Vận dụng – Sáng tạo (Tổng kết chủ đề 6)</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -35506,7 +35449,7 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Tổ chức hoạt động Vận dụng – Sáng tạo</t>
+          <t>Chủ đề 7: Âm nhạc nước ngoài — Vận dụng – Sáng tạo (Tổng kết chủ đề 7)</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
